--- a/excel-files/MARIKINA/PAMANTASAN NG LUNGSOD NG MARIKINA.xlsx
+++ b/excel-files/MARIKINA/PAMANTASAN NG LUNGSOD NG MARIKINA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="25726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29825"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="107" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{118C1C40-8ECA-4B49-8BDC-77A8FC994FB7}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -151,7 +151,19 @@
     <t xml:space="preserve">Quantity based on Target LAS - Q1 </t>
   </si>
   <si>
-    <t>Quantity based on Target LAS - Q3</t>
+    <t>Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS) - Q1</t>
+  </si>
+  <si>
+    <t>Year of Delivery-LAS - Q1</t>
+  </si>
+  <si>
+    <t>SOURCE - LAS (CO,RO, SDO) - Q1</t>
+  </si>
+  <si>
+    <t>GAP - LAS - Q1</t>
+  </si>
+  <si>
+    <t>SURPLUS - LAS - Q1</t>
   </si>
   <si>
     <t>Quantity based on Target LAS - Q2</t>
@@ -163,63 +175,6 @@
     <t>Year of Delivery-LAS Q2</t>
   </si>
   <si>
-    <t>Quantity based on Target LAS - Q4</t>
-  </si>
-  <si>
-    <t>Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS)- Q4</t>
-  </si>
-  <si>
-    <t>Year of Delivery - LAS - Q4</t>
-  </si>
-  <si>
-    <t>Year of Delivery-LAS - Q3</t>
-  </si>
-  <si>
-    <t>Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS) - Q3</t>
-  </si>
-  <si>
-    <t>MAPEH</t>
-  </si>
-  <si>
-    <t>Year of Delivery-LAS - Q1</t>
-  </si>
-  <si>
-    <t>Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS) - Q1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantity based on Target ADM-SLM - Q1 </t>
-  </si>
-  <si>
-    <t>Year of Delivery - ADM-SLM - Q1</t>
-  </si>
-  <si>
-    <t>SOURCE - ADM-SLM (CO,RO, SDO) - Q1</t>
-  </si>
-  <si>
-    <t>Quantity based on Target ADM-SLM - Q2</t>
-  </si>
-  <si>
-    <t>Year of Delivery - ADM-SLM Q2</t>
-  </si>
-  <si>
-    <t>Quantity based on Target ADM-SLM - Q3</t>
-  </si>
-  <si>
-    <t>Year of Delivery - ADM-SLM - Q3</t>
-  </si>
-  <si>
-    <t>Quantity based on Target ADM-SLM - Q4</t>
-  </si>
-  <si>
-    <t>SOURCE - LAS (CO,RO, SDO) - Q1</t>
-  </si>
-  <si>
-    <t>GAP - LAS - Q1</t>
-  </si>
-  <si>
-    <t>SURPLUS - LAS - Q1</t>
-  </si>
-  <si>
     <t>SOURCE-LAS (CO,RO, SDO) Q2</t>
   </si>
   <si>
@@ -227,6 +182,15 @@
   </si>
   <si>
     <t>SURPLUS - LAS -Q2</t>
+  </si>
+  <si>
+    <t>Quantity based on Target LAS - Q3</t>
+  </si>
+  <si>
+    <t>Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS) - Q3</t>
+  </si>
+  <si>
+    <t>Year of Delivery-LAS - Q3</t>
   </si>
   <si>
     <t>SOURCE-LAS (CO,RO, SDO) - Q3</t>
@@ -238,6 +202,15 @@
     <t>SURPLUS - LAS - Q3</t>
   </si>
   <si>
+    <t>Quantity based on Target LAS - Q4</t>
+  </si>
+  <si>
+    <t>Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS)- Q4</t>
+  </si>
+  <si>
+    <t>Year of Delivery - LAS - Q4</t>
+  </si>
+  <si>
     <t>SOURCE - LAS (CO,RO, SDO) - Q4</t>
   </si>
   <si>
@@ -247,19 +220,55 @@
     <t>SURPLUS - LAS - Q4</t>
   </si>
   <si>
+    <t>KINDER</t>
+  </si>
+  <si>
+    <t>MAPEH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity based on Target ADM-SLM - Q1 </t>
+  </si>
+  <si>
+    <t>Quantity of ADM-SLM Received (Quantity received x No. of ADM-SLM) - Q1</t>
+  </si>
+  <si>
+    <t>Year of Delivery - ADM-SLM - Q1</t>
+  </si>
+  <si>
+    <t>SOURCE - ADM-SLM (CO,RO, SDO) - Q1</t>
+  </si>
+  <si>
     <t>GAP - ADM-SLM - Q1</t>
   </si>
   <si>
     <t>SURPLUS - ADM-SLM - Q1</t>
   </si>
   <si>
-    <t>GAP - ADM-SLM - Q2</t>
+    <t>Quantity based on Target ADM-SLM - Q2</t>
+  </si>
+  <si>
+    <t>Quantity of ADM-SLM Received (Quantity received x No. of ADM-SLM) - Q2</t>
+  </si>
+  <si>
+    <t>Year of Delivery - ADM-SLM Q2</t>
   </si>
   <si>
     <t>SOURCE - ADM-SLM (CO,RO, SDO) Q2</t>
   </si>
   <si>
+    <t>GAP - ADM-SLM - Q2</t>
+  </si>
+  <si>
     <t>SURPLUS - ADM-SLM -Q2</t>
+  </si>
+  <si>
+    <t>Quantity based on Target ADM-SLM - Q3</t>
+  </si>
+  <si>
+    <t>Quantity of ADM-SLM Received (Quantity received x No. of ADM-SLM) - Q3</t>
+  </si>
+  <si>
+    <t>Year of Delivery - ADM-SLM - Q3</t>
   </si>
   <si>
     <t>SOURCE - ADM-SLM(CO,RO, SDO) - Q3</t>
@@ -269,6 +278,12 @@
   </si>
   <si>
     <t>SURPLUS - ADM-SLM - Q3</t>
+  </si>
+  <si>
+    <t>Quantity based on Target ADM-SLM - Q4</t>
+  </si>
+  <si>
+    <t>Quantity of ADM-SLM Received (Quantity received x No. of ADM-SLM)- Q4</t>
   </si>
   <si>
     <t>Year of Delivery - ADM-SLM- Q4</t>
@@ -283,22 +298,10 @@
     <t>SURPLUS - ADM-SLM- Q4</t>
   </si>
   <si>
-    <t>Quantity of ADM-SLM Received (Quantity received x No. of ADM-SLM)- Q4</t>
+    <t>PE</t>
   </si>
   <si>
-    <t>Quantity of ADM-SLM Received (Quantity received x No. of ADM-SLM) - Q1</t>
-  </si>
-  <si>
-    <t>Quantity of ADM-SLM Received (Quantity received x No. of ADM-SLM) - Q2</t>
-  </si>
-  <si>
-    <t>Quantity of ADM-SLM Received (Quantity received x No. of ADM-SLM) - Q3</t>
-  </si>
-  <si>
-    <t>KINDER</t>
-  </si>
-  <si>
-    <t>PE</t>
+    <t>Health</t>
   </si>
   <si>
     <t>Music</t>
@@ -306,15 +309,12 @@
   <si>
     <t>Arts</t>
   </si>
-  <si>
-    <t>Health</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -378,26 +378,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Bookman Old Style"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="1"/>
-      <name val="Bookman Old Style"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="15"/>
-      <color theme="1"/>
-      <name val="Bookman Old Style"/>
-      <family val="1"/>
     </font>
     <font>
       <b/>
@@ -645,7 +625,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -708,12 +688,6 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -726,10 +700,7 @@
     <xf numFmtId="0" fontId="6" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -741,51 +712,22 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -794,127 +736,29 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="63">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <name val="Bookman Old Style"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <name val="Bookman Old Style"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="15"/>
-        <color theme="1"/>
-        <name val="Bookman Old Style"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1862,6 +1706,126 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <border outline="0">
         <bottom style="thin">
           <color rgb="FF000000"/>
@@ -1892,13 +1856,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -2977,6 +2934,13 @@
       </border>
     </dxf>
     <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -3013,13 +2977,6 @@
         <top style="thin">
           <color rgb="FF000000"/>
         </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -3062,7 +3019,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}" name="Table2" displayName="Table2" ref="A1:H145" totalsRowShown="0" headerRowDxfId="62" headerRowBorderDxfId="61" tableBorderDxfId="60">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}" name="Table2" displayName="Table2" ref="A1:H145" totalsRowShown="0" headerRowDxfId="62" headerRowBorderDxfId="60" tableBorderDxfId="61">
   <autoFilter ref="A1:H145" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{6C961029-0F4E-47F8-B820-C81BD075C863}" name="Grade Level"/>
@@ -3079,7 +3036,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}" name="Table1" displayName="Table1" ref="A2:AA127" totalsRowShown="0" dataDxfId="58" headerRowBorderDxfId="59" tableBorderDxfId="57">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}" name="Table1" displayName="Table1" ref="A2:AA127" totalsRowShown="0" dataDxfId="59" headerRowBorderDxfId="57" tableBorderDxfId="58">
   <autoFilter ref="A2:AA127" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{451CCD6B-9C4E-44A3-945A-DE807169F46B}" name="Grade Level" dataDxfId="56"/>
@@ -3135,54 +3092,54 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9E6A4DE0-FDA1-4B9F-927F-226E420BA323}" name="Table14" displayName="Table14" ref="A2:AA140" totalsRowShown="0" dataDxfId="28" headerRowBorderDxfId="29" tableBorderDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9E6A4DE0-FDA1-4B9F-927F-226E420BA323}" name="Table14" displayName="Table14" ref="A2:AA140" totalsRowShown="0" dataDxfId="29" headerRowBorderDxfId="27" tableBorderDxfId="28">
   <autoFilter ref="A2:AA140" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
   <tableColumns count="27">
-    <tableColumn id="1" xr3:uid="{4B1B9E16-DDB6-464C-9C72-937B3CB9CE66}" name="Grade Level" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{73AEA048-228E-40E8-B07A-3A7C30BA0DC7}" name="SUBJECTS" dataDxfId="0"/>
-    <tableColumn id="3" xr3:uid="{187AF7E3-9651-4001-B779-AADEF0EAB05A}" name="Enrolment S.Y. 2025-2026 " dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{41F05D2B-5E6F-433A-B62B-2F1726EA10F2}" name="Quantity based on Target ADM-SLM - Q1 " dataDxfId="26">
+    <tableColumn id="1" xr3:uid="{4B1B9E16-DDB6-464C-9C72-937B3CB9CE66}" name="Grade Level" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{73AEA048-228E-40E8-B07A-3A7C30BA0DC7}" name="SUBJECTS" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{187AF7E3-9651-4001-B779-AADEF0EAB05A}" name="Enrolment S.Y. 2025-2026 " dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{41F05D2B-5E6F-433A-B62B-2F1726EA10F2}" name="Quantity based on Target ADM-SLM - Q1 " dataDxfId="23">
       <calculatedColumnFormula>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{CDE5FD66-559D-4D0F-A587-312B6DC04A00}" name="Quantity of ADM-SLM Received (Quantity received x No. of ADM-SLM) - Q1" dataDxfId="25"/>
-    <tableColumn id="6" xr3:uid="{339CCB0D-A0D6-41EF-9023-6B8DF1A1D211}" name="Year of Delivery - ADM-SLM - Q1" dataDxfId="24"/>
-    <tableColumn id="7" xr3:uid="{66966C8F-6B7D-4027-80F0-10F5BEB94C36}" name="SOURCE - ADM-SLM (CO,RO, SDO) - Q1" dataDxfId="23"/>
-    <tableColumn id="8" xr3:uid="{F205DFF0-AD23-4608-82A0-E64C38A40A7F}" name="GAP - ADM-SLM - Q1" dataDxfId="22">
+    <tableColumn id="5" xr3:uid="{CDE5FD66-559D-4D0F-A587-312B6DC04A00}" name="Quantity of ADM-SLM Received (Quantity received x No. of ADM-SLM) - Q1" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{339CCB0D-A0D6-41EF-9023-6B8DF1A1D211}" name="Year of Delivery - ADM-SLM - Q1" dataDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{66966C8F-6B7D-4027-80F0-10F5BEB94C36}" name="SOURCE - ADM-SLM (CO,RO, SDO) - Q1" dataDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{F205DFF0-AD23-4608-82A0-E64C38A40A7F}" name="GAP - ADM-SLM - Q1" dataDxfId="19">
       <calculatedColumnFormula>IF((D3-E3)&lt;0,0,(D3-E3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{A97DBFEB-A833-47C5-A43D-C6E4D77683A6}" name="SURPLUS - ADM-SLM - Q1" dataDxfId="21">
+    <tableColumn id="9" xr3:uid="{A97DBFEB-A833-47C5-A43D-C6E4D77683A6}" name="SURPLUS - ADM-SLM - Q1" dataDxfId="18">
       <calculatedColumnFormula>IF((E3-D3)&lt;0,0,(E3-D3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{6A093D68-BC9F-46BB-AC8F-CA208309466C}" name="Quantity based on Target ADM-SLM - Q2" dataDxfId="20">
+    <tableColumn id="10" xr3:uid="{6A093D68-BC9F-46BB-AC8F-CA208309466C}" name="Quantity based on Target ADM-SLM - Q2" dataDxfId="17">
       <calculatedColumnFormula>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{CB914A26-115B-4765-A39C-5A2824E73671}" name="Quantity of ADM-SLM Received (Quantity received x No. of ADM-SLM) - Q2" dataDxfId="19"/>
-    <tableColumn id="12" xr3:uid="{35FFB32F-868E-4FBD-946A-0482CC3DE0D4}" name="Year of Delivery - ADM-SLM Q2" dataDxfId="18"/>
-    <tableColumn id="13" xr3:uid="{987FB8ED-06DA-4311-80C5-DAF78B602129}" name="SOURCE - ADM-SLM (CO,RO, SDO) Q2" dataDxfId="17"/>
-    <tableColumn id="14" xr3:uid="{24CC35CF-2900-4C84-934F-7E29CCFCCEC9}" name="GAP - ADM-SLM - Q2" dataDxfId="16"/>
-    <tableColumn id="15" xr3:uid="{0DA82B8D-6A8D-469A-8302-7E7DD0B1BDC4}" name="SURPLUS - ADM-SLM -Q2" dataDxfId="15"/>
-    <tableColumn id="16" xr3:uid="{126A7F40-0CC3-4264-A57D-D7C0C9FE4720}" name="Quantity based on Target ADM-SLM - Q3" dataDxfId="14">
+    <tableColumn id="11" xr3:uid="{CB914A26-115B-4765-A39C-5A2824E73671}" name="Quantity of ADM-SLM Received (Quantity received x No. of ADM-SLM) - Q2" dataDxfId="16"/>
+    <tableColumn id="12" xr3:uid="{35FFB32F-868E-4FBD-946A-0482CC3DE0D4}" name="Year of Delivery - ADM-SLM Q2" dataDxfId="15"/>
+    <tableColumn id="13" xr3:uid="{987FB8ED-06DA-4311-80C5-DAF78B602129}" name="SOURCE - ADM-SLM (CO,RO, SDO) Q2" dataDxfId="14"/>
+    <tableColumn id="14" xr3:uid="{24CC35CF-2900-4C84-934F-7E29CCFCCEC9}" name="GAP - ADM-SLM - Q2" dataDxfId="13"/>
+    <tableColumn id="15" xr3:uid="{0DA82B8D-6A8D-469A-8302-7E7DD0B1BDC4}" name="SURPLUS - ADM-SLM -Q2" dataDxfId="12"/>
+    <tableColumn id="16" xr3:uid="{126A7F40-0CC3-4264-A57D-D7C0C9FE4720}" name="Quantity based on Target ADM-SLM - Q3" dataDxfId="11">
       <calculatedColumnFormula>#REF!*8</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{711B70A4-2160-43C1-900D-FD892755D7AB}" name="Quantity of ADM-SLM Received (Quantity received x No. of ADM-SLM) - Q3" dataDxfId="13"/>
-    <tableColumn id="18" xr3:uid="{D8C99A72-7FED-4E85-8CB4-4A08C56BCB15}" name="Year of Delivery - ADM-SLM - Q3" dataDxfId="12"/>
-    <tableColumn id="19" xr3:uid="{D48A881D-138B-4288-AA57-050C0AE3F5F6}" name="SOURCE - ADM-SLM(CO,RO, SDO) - Q3" dataDxfId="11"/>
-    <tableColumn id="20" xr3:uid="{B03A44EC-B25E-4D0D-B9E6-71825AC6E51F}" name="GAP - ADM-SLM - Q3" dataDxfId="10">
+    <tableColumn id="17" xr3:uid="{711B70A4-2160-43C1-900D-FD892755D7AB}" name="Quantity of ADM-SLM Received (Quantity received x No. of ADM-SLM) - Q3" dataDxfId="10"/>
+    <tableColumn id="18" xr3:uid="{D8C99A72-7FED-4E85-8CB4-4A08C56BCB15}" name="Year of Delivery - ADM-SLM - Q3" dataDxfId="9"/>
+    <tableColumn id="19" xr3:uid="{D48A881D-138B-4288-AA57-050C0AE3F5F6}" name="SOURCE - ADM-SLM(CO,RO, SDO) - Q3" dataDxfId="8"/>
+    <tableColumn id="20" xr3:uid="{B03A44EC-B25E-4D0D-B9E6-71825AC6E51F}" name="GAP - ADM-SLM - Q3" dataDxfId="7">
       <calculatedColumnFormula>IF((P3-Q3)&lt;0,0,(P3-Q3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{3338E724-88DC-45DA-8F55-7AAE5A560621}" name="SURPLUS - ADM-SLM - Q3" dataDxfId="9">
+    <tableColumn id="21" xr3:uid="{3338E724-88DC-45DA-8F55-7AAE5A560621}" name="SURPLUS - ADM-SLM - Q3" dataDxfId="6">
       <calculatedColumnFormula>IF((Q3-P3)&lt;0,0,(Q3-P3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{AC55FA3C-A61A-4AB0-8391-EC237845F1BF}" name="Quantity based on Target ADM-SLM - Q4" dataDxfId="8">
+    <tableColumn id="22" xr3:uid="{AC55FA3C-A61A-4AB0-8391-EC237845F1BF}" name="Quantity based on Target ADM-SLM - Q4" dataDxfId="5">
       <calculatedColumnFormula>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{D3F77FA4-2477-4BAF-A6FD-8446908907B9}" name="Quantity of ADM-SLM Received (Quantity received x No. of ADM-SLM)- Q4" dataDxfId="7"/>
-    <tableColumn id="24" xr3:uid="{C66CE0BE-6DCF-4E05-9DBD-D908450B3841}" name="Year of Delivery - ADM-SLM- Q4" dataDxfId="6"/>
-    <tableColumn id="25" xr3:uid="{AABA2263-B244-4CBF-87B1-CDAAECF763E4}" name="SOURCE - ADM-SLM - (CO,RO, SDO) - Q4" dataDxfId="5"/>
-    <tableColumn id="26" xr3:uid="{21E1F5D8-F09B-453A-90E6-AA7B2E8821D1}" name="GAP - ADM-SLM - Q4" dataDxfId="4">
+    <tableColumn id="23" xr3:uid="{D3F77FA4-2477-4BAF-A6FD-8446908907B9}" name="Quantity of ADM-SLM Received (Quantity received x No. of ADM-SLM)- Q4" dataDxfId="4"/>
+    <tableColumn id="24" xr3:uid="{C66CE0BE-6DCF-4E05-9DBD-D908450B3841}" name="Year of Delivery - ADM-SLM- Q4" dataDxfId="3"/>
+    <tableColumn id="25" xr3:uid="{AABA2263-B244-4CBF-87B1-CDAAECF763E4}" name="SOURCE - ADM-SLM - (CO,RO, SDO) - Q4" dataDxfId="2"/>
+    <tableColumn id="26" xr3:uid="{21E1F5D8-F09B-453A-90E6-AA7B2E8821D1}" name="GAP - ADM-SLM - Q4" dataDxfId="1">
       <calculatedColumnFormula>IF((V3-W3)&lt;0,0,(V3-W3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{67725D86-C1DE-4DB2-8FBD-99B8821906AB}" name="SURPLUS - ADM-SLM- Q4" dataDxfId="3">
+    <tableColumn id="27" xr3:uid="{67725D86-C1DE-4DB2-8FBD-99B8821906AB}" name="SURPLUS - ADM-SLM- Q4" dataDxfId="0">
       <calculatedColumnFormula>IF((W3-V3)&lt;0,0,(W3-V3))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3508,17 +3465,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H98"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.8984375" customWidth="1"/>
-    <col min="3" max="5" width="24.8984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.09765625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.09765625" customWidth="1"/>
-    <col min="8" max="8" width="16.09765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.85546875" customWidth="1"/>
+    <col min="3" max="5" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" customWidth="1"/>
+    <col min="8" max="8" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="14" customFormat="1" ht="64.95" customHeight="1">
+    <row r="1" spans="1:8" s="14" customFormat="1" ht="64.900000000000006" customHeight="1">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -3624,7 +3581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="19.2">
+    <row r="6" spans="1:8" ht="19.149999999999999">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -3729,7 +3686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="19.2">
+    <row r="12" spans="1:8" ht="19.149999999999999">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -3854,7 +3811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="19.2">
+    <row r="19" spans="1:8" ht="19.149999999999999">
       <c r="A19" s="1">
         <v>3</v>
       </c>
@@ -3924,7 +3881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="19.2">
+    <row r="23" spans="1:8" ht="19.149999999999999">
       <c r="A23" s="1">
         <v>4</v>
       </c>
@@ -5381,8 +5338,8 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E2:E6 E8:E12 E14:E19 E21:E29 E31:E39 E41:E49 E51:E59 E61:E69 E71:E79 E81:E89" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025 ,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
@@ -5397,68 +5354,68 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <dimension ref="A1:AA127"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="9.3984375" customWidth="1"/>
-    <col min="2" max="2" width="27.8984375" customWidth="1"/>
-    <col min="3" max="3" width="17.19921875" customWidth="1"/>
-    <col min="4" max="4" width="26.19921875" customWidth="1"/>
-    <col min="5" max="5" width="23.19921875" customWidth="1"/>
-    <col min="6" max="6" width="24.8984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.59765625" customWidth="1"/>
-    <col min="8" max="9" width="20.8984375" customWidth="1"/>
-    <col min="10" max="10" width="13.69921875" customWidth="1"/>
-    <col min="11" max="11" width="35.59765625" customWidth="1"/>
-    <col min="12" max="12" width="24.8984375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="31.59765625" customWidth="1"/>
-    <col min="14" max="15" width="20.8984375" customWidth="1"/>
-    <col min="16" max="16" width="21.59765625" customWidth="1"/>
-    <col min="17" max="17" width="33.3984375" customWidth="1"/>
-    <col min="18" max="18" width="25.796875" customWidth="1"/>
-    <col min="19" max="19" width="32.8984375" customWidth="1"/>
-    <col min="20" max="21" width="20.8984375" customWidth="1"/>
-    <col min="22" max="22" width="16.19921875" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" customWidth="1"/>
+    <col min="2" max="2" width="27.85546875" customWidth="1"/>
+    <col min="3" max="3" width="17.140625" customWidth="1"/>
+    <col min="4" max="4" width="26.140625" customWidth="1"/>
+    <col min="5" max="5" width="23.140625" customWidth="1"/>
+    <col min="6" max="6" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5703125" customWidth="1"/>
+    <col min="8" max="9" width="20.85546875" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" customWidth="1"/>
+    <col min="11" max="11" width="35.5703125" customWidth="1"/>
+    <col min="12" max="12" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="31.5703125" customWidth="1"/>
+    <col min="14" max="15" width="20.85546875" customWidth="1"/>
+    <col min="16" max="16" width="21.5703125" customWidth="1"/>
+    <col min="17" max="17" width="33.42578125" customWidth="1"/>
+    <col min="18" max="18" width="25.85546875" customWidth="1"/>
+    <col min="19" max="19" width="32.85546875" customWidth="1"/>
+    <col min="20" max="21" width="20.85546875" customWidth="1"/>
+    <col min="22" max="22" width="16.140625" customWidth="1"/>
     <col min="23" max="23" width="25" customWidth="1"/>
-    <col min="24" max="24" width="15.296875" customWidth="1"/>
-    <col min="25" max="25" width="20.796875" customWidth="1"/>
-    <col min="26" max="26" width="14.796875" customWidth="1"/>
-    <col min="27" max="27" width="15.19921875" customWidth="1"/>
+    <col min="24" max="24" width="15.28515625" customWidth="1"/>
+    <col min="25" max="25" width="20.85546875" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" customWidth="1"/>
+    <col min="27" max="27" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="31" customFormat="1" ht="34.200000000000003" customHeight="1">
-      <c r="D1" s="38" t="s">
+    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
+      <c r="D1" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="39" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
-      <c r="N1" s="39"/>
-      <c r="O1" s="39"/>
-      <c r="P1" s="40" t="s">
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="Q1" s="40"/>
-      <c r="R1" s="40"/>
-      <c r="S1" s="40"/>
-      <c r="T1" s="40"/>
-      <c r="U1" s="40"/>
-      <c r="V1" s="41" t="s">
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="44"/>
+      <c r="V1" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="W1" s="41"/>
-      <c r="X1" s="41"/>
-      <c r="Y1" s="41"/>
-      <c r="Z1" s="41"/>
-      <c r="AA1" s="41"/>
+      <c r="W1" s="45"/>
+      <c r="X1" s="45"/>
+      <c r="Y1" s="45"/>
+      <c r="Z1" s="45"/>
+      <c r="AA1" s="45"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -5474,103 +5431,103 @@
         <v>36</v>
       </c>
       <c r="E2" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="I2" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="J2" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="K2" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="L2" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="M2" s="40" t="s">
+        <v>45</v>
+      </c>
+      <c r="N2" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="F2" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="G2" s="26" t="s">
+      <c r="Q2" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="T2" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="U2" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="V2" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="W2" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="X2" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y2" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="H2" s="25" t="s">
+      <c r="Z2" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="I2" s="26" t="s">
+      <c r="AA2" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="J2" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="K2" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="L2" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="M2" s="24" t="s">
+    </row>
+    <row r="3" spans="1:27" ht="30.6" customHeight="1">
+      <c r="A3" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="N2" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="O2" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="P2" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q2" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="R2" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="S2" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="T2" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="U2" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="V2" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="W2" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="X2" s="29" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y2" s="30" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z2" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA2" s="28" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="30.6" customHeight="1">
-      <c r="A3" s="53" t="s">
-        <v>85</v>
-      </c>
-      <c r="B3" s="43"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="44">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E3" s="44"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="45">
+      <c r="B3" s="33"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="34">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="34"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34">
         <f>IF((D3-E3)&lt;0,0,(D3-E3))</f>
         <v>0</v>
       </c>
-      <c r="I3" s="45">
+      <c r="I3" s="34">
         <f>IF((E3-D3)&lt;0,0,(E3-D3))</f>
         <v>0</v>
       </c>
-      <c r="J3" s="44">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K3" s="44"/>
-      <c r="L3" s="42"/>
-      <c r="M3" s="44"/>
+      <c r="J3" s="34">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="K3" s="34"/>
+      <c r="L3" s="32"/>
+      <c r="M3" s="34"/>
       <c r="N3" s="5">
         <f t="shared" ref="N3" si="0">IF((J3-K3)&lt;0,0,(J3-K3))</f>
         <v>0</v>
@@ -5583,34 +5540,34 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q3" s="44"/>
-      <c r="R3" s="42"/>
-      <c r="S3" s="44"/>
-      <c r="T3" s="44">
+      <c r="Q3" s="34"/>
+      <c r="R3" s="32"/>
+      <c r="S3" s="34"/>
+      <c r="T3" s="34">
         <f>IF((P3-Q3)&lt;0,0,(P3-Q3))</f>
         <v>0</v>
       </c>
-      <c r="U3" s="44">
+      <c r="U3" s="34">
         <f>IF((Q3-P3)&lt;0,0,(Q3-P3))</f>
         <v>0</v>
       </c>
-      <c r="V3" s="44">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W3" s="44"/>
-      <c r="X3" s="42"/>
-      <c r="Y3" s="44"/>
-      <c r="Z3" s="44">
+      <c r="V3" s="34">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="W3" s="34"/>
+      <c r="X3" s="32"/>
+      <c r="Y3" s="34"/>
+      <c r="Z3" s="34">
         <f>IF((V3-W3)&lt;0,0,(V3-W3))</f>
         <v>0</v>
       </c>
-      <c r="AA3" s="44">
+      <c r="AA3" s="34">
         <f>IF((W3-V3)&lt;0,0,(W3-V3))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" s="7" customFormat="1" ht="19.2">
+    <row r="4" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J4" s="13"/>
       <c r="N4" s="13"/>
       <c r="O4" s="13"/>
@@ -5622,7 +5579,7 @@
       <c r="Z4" s="13"/>
       <c r="AA4" s="13"/>
     </row>
-    <row r="5" spans="1:27" ht="19.2">
+    <row r="5" spans="1:27" ht="19.149999999999999">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -5691,7 +5648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.2">
+    <row r="6" spans="1:27" ht="19.149999999999999">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -5760,7 +5717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.2">
+    <row r="7" spans="1:27" ht="19.149999999999999">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -5829,7 +5786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.2">
+    <row r="8" spans="1:27" ht="19.149999999999999">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -5898,7 +5855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.2">
+    <row r="9" spans="1:27" ht="19.149999999999999">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -5967,26 +5924,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.2">
-      <c r="A10" s="35">
+    <row r="10" spans="1:27" ht="19.149999999999999">
+      <c r="A10" s="1">
         <v>1</v>
       </c>
-      <c r="B10" s="36" t="s">
+      <c r="B10" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="35"/>
-      <c r="D10" s="37">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="37"/>
-      <c r="F10" s="35"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="5"/>
+      <c r="F10" s="1"/>
       <c r="G10" s="5"/>
-      <c r="H10" s="37">
+      <c r="H10" s="5">
         <f>IF((D10-E10)&lt;0,0,(D10-E10))</f>
         <v>0</v>
       </c>
-      <c r="I10" s="37">
+      <c r="I10" s="5">
         <f>IF((E10-D10)&lt;0,0,(E10-D10))</f>
         <v>0</v>
       </c>
@@ -5994,8 +5951,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K10" s="37"/>
-      <c r="L10" s="35"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="1"/>
       <c r="M10" s="5"/>
       <c r="N10" s="5">
         <f t="shared" si="10"/>
@@ -6009,8 +5966,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q10" s="37"/>
-      <c r="R10" s="35"/>
+      <c r="Q10" s="5"/>
+      <c r="R10" s="1"/>
       <c r="S10" s="5"/>
       <c r="T10" s="5">
         <f t="shared" si="12"/>
@@ -6024,8 +5981,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W10" s="37"/>
-      <c r="X10" s="35"/>
+      <c r="W10" s="5"/>
+      <c r="X10" s="1"/>
       <c r="Y10" s="5"/>
       <c r="Z10" s="5">
         <f t="shared" si="14"/>
@@ -6036,26 +5993,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="19.2">
-      <c r="A11" s="35">
+    <row r="11" spans="1:27" ht="19.149999999999999">
+      <c r="A11" s="1">
         <v>1</v>
       </c>
-      <c r="B11" s="36" t="s">
+      <c r="B11" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="35"/>
-      <c r="D11" s="37">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="37"/>
-      <c r="F11" s="35"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="5"/>
+      <c r="F11" s="1"/>
       <c r="G11" s="5"/>
-      <c r="H11" s="37">
+      <c r="H11" s="5">
         <f>IF((D11-E11)&lt;0,0,(D11-E11))</f>
         <v>0</v>
       </c>
-      <c r="I11" s="37">
+      <c r="I11" s="5">
         <f>IF((E11-D11)&lt;0,0,(E11-D11))</f>
         <v>0</v>
       </c>
@@ -6063,8 +6020,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K11" s="37"/>
-      <c r="L11" s="35"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="1"/>
       <c r="M11" s="5"/>
       <c r="N11" s="5">
         <f t="shared" si="10"/>
@@ -6078,8 +6035,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q11" s="37"/>
-      <c r="R11" s="35"/>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="1"/>
       <c r="S11" s="5"/>
       <c r="T11" s="5">
         <f t="shared" si="12"/>
@@ -6093,8 +6050,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W11" s="37"/>
-      <c r="X11" s="35"/>
+      <c r="W11" s="5"/>
+      <c r="X11" s="1"/>
       <c r="Y11" s="5"/>
       <c r="Z11" s="5">
         <f t="shared" si="14"/>
@@ -6105,26 +6062,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="19.2">
-      <c r="A12" s="35">
+    <row r="12" spans="1:27" ht="19.149999999999999">
+      <c r="A12" s="1">
         <v>1</v>
       </c>
-      <c r="B12" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" s="35"/>
-      <c r="D12" s="37">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E12" s="37"/>
-      <c r="F12" s="35"/>
+      <c r="B12" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="5"/>
+      <c r="F12" s="1"/>
       <c r="G12" s="5"/>
-      <c r="H12" s="37">
+      <c r="H12" s="5">
         <f>IF((D12-E12)&lt;0,0,(D12-E12))</f>
         <v>0</v>
       </c>
-      <c r="I12" s="37">
+      <c r="I12" s="5">
         <f>IF((E12-D12)&lt;0,0,(E12-D12))</f>
         <v>0</v>
       </c>
@@ -6132,8 +6089,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K12" s="37"/>
-      <c r="L12" s="35"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="1"/>
       <c r="M12" s="5"/>
       <c r="N12" s="5">
         <f t="shared" si="10"/>
@@ -6147,8 +6104,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q12" s="37"/>
-      <c r="R12" s="35"/>
+      <c r="Q12" s="5"/>
+      <c r="R12" s="1"/>
       <c r="S12" s="5"/>
       <c r="T12" s="5">
         <f t="shared" si="12"/>
@@ -6162,8 +6119,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W12" s="37"/>
-      <c r="X12" s="35"/>
+      <c r="W12" s="5"/>
+      <c r="X12" s="1"/>
       <c r="Y12" s="5"/>
       <c r="Z12" s="5">
         <f t="shared" si="14"/>
@@ -6174,7 +6131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" s="7" customFormat="1" ht="19.2">
+    <row r="13" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J13" s="13"/>
       <c r="N13" s="13"/>
       <c r="O13" s="13"/>
@@ -6187,7 +6144,7 @@
       <c r="Z13" s="13"/>
       <c r="AA13" s="13"/>
     </row>
-    <row r="14" spans="1:27" ht="19.2">
+    <row r="14" spans="1:27" ht="19.149999999999999">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -6256,7 +6213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.2">
+    <row r="15" spans="1:27" ht="19.149999999999999">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -6325,7 +6282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.2">
+    <row r="16" spans="1:27" ht="19.149999999999999">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -6394,7 +6351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.2">
+    <row r="17" spans="1:27" ht="19.149999999999999">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -6463,7 +6420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.2">
+    <row r="18" spans="1:27" ht="19.149999999999999">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -6532,26 +6489,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.2">
-      <c r="A19" s="35">
+    <row r="19" spans="1:27" ht="19.149999999999999">
+      <c r="A19" s="1">
         <v>2</v>
       </c>
-      <c r="B19" s="36" t="s">
+      <c r="B19" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="35"/>
-      <c r="D19" s="37">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E19" s="37"/>
-      <c r="F19" s="35"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="5"/>
+      <c r="F19" s="1"/>
       <c r="G19" s="5"/>
-      <c r="H19" s="37">
+      <c r="H19" s="5">
         <f>IF((D19-E19)&lt;0,0,(D19-E19))</f>
         <v>0</v>
       </c>
-      <c r="I19" s="37">
+      <c r="I19" s="5">
         <f>IF((E19-D19)&lt;0,0,(E19-D19))</f>
         <v>0</v>
       </c>
@@ -6559,8 +6516,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K19" s="37"/>
-      <c r="L19" s="35"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="1"/>
       <c r="M19" s="5"/>
       <c r="N19" s="5">
         <f t="shared" si="10"/>
@@ -6574,8 +6531,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q19" s="37"/>
-      <c r="R19" s="35"/>
+      <c r="Q19" s="5"/>
+      <c r="R19" s="1"/>
       <c r="S19" s="5"/>
       <c r="T19" s="5">
         <f t="shared" si="12"/>
@@ -6589,8 +6546,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W19" s="37"/>
-      <c r="X19" s="35"/>
+      <c r="W19" s="5"/>
+      <c r="X19" s="1"/>
       <c r="Y19" s="5"/>
       <c r="Z19" s="5">
         <f t="shared" si="14"/>
@@ -6601,26 +6558,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="19.2">
-      <c r="A20" s="35">
+    <row r="20" spans="1:27" ht="19.149999999999999">
+      <c r="A20" s="1">
         <v>2</v>
       </c>
-      <c r="B20" s="36" t="s">
+      <c r="B20" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="35"/>
-      <c r="D20" s="37">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E20" s="37"/>
-      <c r="F20" s="35"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E20" s="5"/>
+      <c r="F20" s="1"/>
       <c r="G20" s="5"/>
-      <c r="H20" s="37">
+      <c r="H20" s="5">
         <f>IF((D20-E20)&lt;0,0,(D20-E20))</f>
         <v>0</v>
       </c>
-      <c r="I20" s="37">
+      <c r="I20" s="5">
         <f>IF((E20-D20)&lt;0,0,(E20-D20))</f>
         <v>0</v>
       </c>
@@ -6628,8 +6585,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K20" s="37"/>
-      <c r="L20" s="35"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="1"/>
       <c r="M20" s="5"/>
       <c r="N20" s="5">
         <f t="shared" si="10"/>
@@ -6643,8 +6600,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q20" s="37"/>
-      <c r="R20" s="35"/>
+      <c r="Q20" s="5"/>
+      <c r="R20" s="1"/>
       <c r="S20" s="5"/>
       <c r="T20" s="5">
         <f t="shared" si="12"/>
@@ -6658,8 +6615,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W20" s="37"/>
-      <c r="X20" s="35"/>
+      <c r="W20" s="5"/>
+      <c r="X20" s="1"/>
       <c r="Y20" s="5"/>
       <c r="Z20" s="5">
         <f t="shared" si="14"/>
@@ -6670,26 +6627,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="19.2">
-      <c r="A21" s="35">
+    <row r="21" spans="1:27" ht="19.149999999999999">
+      <c r="A21" s="1">
         <v>2</v>
       </c>
-      <c r="B21" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="C21" s="35"/>
-      <c r="D21" s="37">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E21" s="37"/>
-      <c r="F21" s="35"/>
+      <c r="B21" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" s="1"/>
+      <c r="D21" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="5"/>
+      <c r="F21" s="1"/>
       <c r="G21" s="5"/>
-      <c r="H21" s="37">
+      <c r="H21" s="5">
         <f>IF((D21-E21)&lt;0,0,(D21-E21))</f>
         <v>0</v>
       </c>
-      <c r="I21" s="37">
+      <c r="I21" s="5">
         <f>IF((E21-D21)&lt;0,0,(E21-D21))</f>
         <v>0</v>
       </c>
@@ -6697,8 +6654,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K21" s="37"/>
-      <c r="L21" s="35"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="1"/>
       <c r="M21" s="5"/>
       <c r="N21" s="5">
         <f t="shared" si="10"/>
@@ -6712,8 +6669,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q21" s="37"/>
-      <c r="R21" s="35"/>
+      <c r="Q21" s="5"/>
+      <c r="R21" s="1"/>
       <c r="S21" s="5"/>
       <c r="T21" s="5">
         <f t="shared" si="12"/>
@@ -6727,8 +6684,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W21" s="37"/>
-      <c r="X21" s="35"/>
+      <c r="W21" s="5"/>
+      <c r="X21" s="1"/>
       <c r="Y21" s="5"/>
       <c r="Z21" s="5">
         <f t="shared" si="14"/>
@@ -6739,7 +6696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" s="7" customFormat="1" ht="19.2">
+    <row r="22" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J22" s="13"/>
       <c r="M22" s="5"/>
       <c r="N22" s="13"/>
@@ -6753,7 +6710,7 @@
       <c r="Z22" s="13"/>
       <c r="AA22" s="13"/>
     </row>
-    <row r="23" spans="1:27" ht="19.2">
+    <row r="23" spans="1:27" ht="19.149999999999999">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -6822,7 +6779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.2">
+    <row r="24" spans="1:27" ht="19.149999999999999">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -6891,7 +6848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.2">
+    <row r="25" spans="1:27" ht="19.149999999999999">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -6960,7 +6917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.2">
+    <row r="26" spans="1:27" ht="19.149999999999999">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -7029,7 +6986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.2">
+    <row r="27" spans="1:27" ht="19.149999999999999">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -7098,7 +7055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.2">
+    <row r="28" spans="1:27" ht="19.149999999999999">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -7167,26 +7124,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.2">
-      <c r="A29" s="35">
+    <row r="29" spans="1:27" ht="19.149999999999999">
+      <c r="A29" s="1">
         <v>3</v>
       </c>
-      <c r="B29" s="36" t="s">
+      <c r="B29" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C29" s="35"/>
-      <c r="D29" s="37">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E29" s="37"/>
-      <c r="F29" s="35"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="5"/>
+      <c r="F29" s="1"/>
       <c r="G29" s="5"/>
-      <c r="H29" s="37">
+      <c r="H29" s="5">
         <f>IF((D29-E29)&lt;0,0,(D29-E29))</f>
         <v>0</v>
       </c>
-      <c r="I29" s="37">
+      <c r="I29" s="5">
         <f>IF((E29-D29)&lt;0,0,(E29-D29))</f>
         <v>0</v>
       </c>
@@ -7194,8 +7151,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K29" s="37"/>
-      <c r="L29" s="35"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="1"/>
       <c r="M29" s="5"/>
       <c r="N29" s="5">
         <f t="shared" si="10"/>
@@ -7209,8 +7166,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q29" s="37"/>
-      <c r="R29" s="35"/>
+      <c r="Q29" s="5"/>
+      <c r="R29" s="1"/>
       <c r="S29" s="5"/>
       <c r="T29" s="5">
         <f t="shared" si="12"/>
@@ -7224,8 +7181,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W29" s="37"/>
-      <c r="X29" s="35"/>
+      <c r="W29" s="5"/>
+      <c r="X29" s="1"/>
       <c r="Y29" s="5"/>
       <c r="Z29" s="5">
         <f t="shared" si="14"/>
@@ -7236,26 +7193,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="19.2">
-      <c r="A30" s="35">
+    <row r="30" spans="1:27" ht="19.149999999999999">
+      <c r="A30" s="1">
         <v>3</v>
       </c>
-      <c r="B30" s="36" t="s">
+      <c r="B30" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="35"/>
-      <c r="D30" s="37">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E30" s="37"/>
-      <c r="F30" s="35"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="5"/>
+      <c r="F30" s="1"/>
       <c r="G30" s="5"/>
-      <c r="H30" s="37">
+      <c r="H30" s="5">
         <f>IF((D30-E30)&lt;0,0,(D30-E30))</f>
         <v>0</v>
       </c>
-      <c r="I30" s="37">
+      <c r="I30" s="5">
         <f>IF((E30-D30)&lt;0,0,(E30-D30))</f>
         <v>0</v>
       </c>
@@ -7263,8 +7220,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K30" s="37"/>
-      <c r="L30" s="35"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="1"/>
       <c r="M30" s="5"/>
       <c r="N30" s="5">
         <f t="shared" si="10"/>
@@ -7278,8 +7235,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q30" s="37"/>
-      <c r="R30" s="35"/>
+      <c r="Q30" s="5"/>
+      <c r="R30" s="1"/>
       <c r="S30" s="5"/>
       <c r="T30" s="5">
         <f t="shared" si="12"/>
@@ -7293,8 +7250,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W30" s="37"/>
-      <c r="X30" s="35"/>
+      <c r="W30" s="5"/>
+      <c r="X30" s="1"/>
       <c r="Y30" s="5"/>
       <c r="Z30" s="5">
         <f t="shared" si="14"/>
@@ -7305,26 +7262,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="19.2">
-      <c r="A31" s="35">
+    <row r="31" spans="1:27" ht="19.149999999999999">
+      <c r="A31" s="1">
         <v>3</v>
       </c>
-      <c r="B31" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="C31" s="35"/>
-      <c r="D31" s="37">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E31" s="37"/>
-      <c r="F31" s="35"/>
+      <c r="B31" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31" s="1"/>
+      <c r="D31" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E31" s="5"/>
+      <c r="F31" s="1"/>
       <c r="G31" s="5"/>
-      <c r="H31" s="37">
+      <c r="H31" s="5">
         <f>IF((D31-E31)&lt;0,0,(D31-E31))</f>
         <v>0</v>
       </c>
-      <c r="I31" s="37">
+      <c r="I31" s="5">
         <f>IF((E31-D31)&lt;0,0,(E31-D31))</f>
         <v>0</v>
       </c>
@@ -7332,8 +7289,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K31" s="37"/>
-      <c r="L31" s="35"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="1"/>
       <c r="M31" s="5"/>
       <c r="N31" s="5">
         <f t="shared" si="10"/>
@@ -7347,8 +7304,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q31" s="37"/>
-      <c r="R31" s="35"/>
+      <c r="Q31" s="5"/>
+      <c r="R31" s="1"/>
       <c r="S31" s="5"/>
       <c r="T31" s="5">
         <f t="shared" si="12"/>
@@ -7362,8 +7319,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W31" s="37"/>
-      <c r="X31" s="35"/>
+      <c r="W31" s="5"/>
+      <c r="X31" s="1"/>
       <c r="Y31" s="5"/>
       <c r="Z31" s="5">
         <f t="shared" si="14"/>
@@ -7374,7 +7331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" s="7" customFormat="1" ht="19.2">
+    <row r="32" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J32" s="13"/>
       <c r="M32" s="5"/>
       <c r="N32" s="13"/>
@@ -7388,7 +7345,7 @@
       <c r="Z32" s="13"/>
       <c r="AA32" s="13"/>
     </row>
-    <row r="33" spans="1:27" ht="19.2">
+    <row r="33" spans="1:27" ht="19.149999999999999">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -7457,7 +7414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.2">
+    <row r="34" spans="1:27" ht="19.149999999999999">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -7526,7 +7483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.2">
+    <row r="35" spans="1:27" ht="19.149999999999999">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -7595,7 +7552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.2">
+    <row r="36" spans="1:27" ht="19.149999999999999">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -7664,7 +7621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.2">
+    <row r="37" spans="1:27" ht="19.149999999999999">
       <c r="A37" s="1">
         <v>4</v>
       </c>
@@ -7733,7 +7690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.2">
+    <row r="38" spans="1:27" ht="19.149999999999999">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -7802,7 +7759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.2">
+    <row r="39" spans="1:27" ht="19.149999999999999">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -7871,7 +7828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.2">
+    <row r="40" spans="1:27" ht="19.149999999999999">
       <c r="A40" s="1">
         <v>4</v>
       </c>
@@ -7940,7 +7897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.2">
+    <row r="41" spans="1:27" ht="19.149999999999999">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -8009,7 +7966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1" ht="19.2">
+    <row r="42" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J42" s="13"/>
       <c r="M42" s="5"/>
       <c r="N42" s="13"/>
@@ -8023,7 +7980,7 @@
       <c r="Z42" s="13"/>
       <c r="AA42" s="13"/>
     </row>
-    <row r="43" spans="1:27" ht="19.2">
+    <row r="43" spans="1:27" ht="19.149999999999999">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -8092,7 +8049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.2">
+    <row r="44" spans="1:27" ht="19.149999999999999">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -8161,7 +8118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.2">
+    <row r="45" spans="1:27" ht="19.149999999999999">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -8230,7 +8187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.2">
+    <row r="46" spans="1:27" ht="19.149999999999999">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -8299,7 +8256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.2">
+    <row r="47" spans="1:27" ht="19.149999999999999">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -8368,7 +8325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.2">
+    <row r="48" spans="1:27" ht="19.149999999999999">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -8437,7 +8394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.2">
+    <row r="49" spans="1:27" ht="19.149999999999999">
       <c r="A49" s="1">
         <v>5</v>
       </c>
@@ -8506,7 +8463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.2">
+    <row r="50" spans="1:27" ht="19.149999999999999">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -8575,7 +8532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.2">
+    <row r="51" spans="1:27" ht="19.149999999999999">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -8644,7 +8601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" s="7" customFormat="1" ht="19.2">
+    <row r="52" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J52" s="13"/>
       <c r="M52" s="5"/>
       <c r="N52" s="13"/>
@@ -8658,7 +8615,7 @@
       <c r="Z52" s="13"/>
       <c r="AA52" s="13"/>
     </row>
-    <row r="53" spans="1:27" ht="19.2">
+    <row r="53" spans="1:27" ht="19.149999999999999">
       <c r="A53" s="1">
         <v>6</v>
       </c>
@@ -8727,7 +8684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="19.2">
+    <row r="54" spans="1:27" ht="19.149999999999999">
       <c r="A54" s="1">
         <v>6</v>
       </c>
@@ -8796,7 +8753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="19.2">
+    <row r="55" spans="1:27" ht="19.149999999999999">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -8865,7 +8822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.2">
+    <row r="56" spans="1:27" ht="19.149999999999999">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -8934,7 +8891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.2">
+    <row r="57" spans="1:27" ht="19.149999999999999">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -9003,7 +8960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.2">
+    <row r="58" spans="1:27" ht="19.149999999999999">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -9072,7 +9029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.2">
+    <row r="59" spans="1:27" ht="19.149999999999999">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -9141,7 +9098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.2">
+    <row r="60" spans="1:27" ht="19.149999999999999">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -9210,7 +9167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.2">
+    <row r="61" spans="1:27" ht="19.149999999999999">
       <c r="A61" s="1">
         <v>6</v>
       </c>
@@ -9279,7 +9236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" s="7" customFormat="1" ht="19.2">
+    <row r="62" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J62" s="13"/>
       <c r="M62" s="5"/>
       <c r="N62" s="13"/>
@@ -9293,7 +9250,7 @@
       <c r="Z62" s="13"/>
       <c r="AA62" s="13"/>
     </row>
-    <row r="63" spans="1:27" ht="19.2">
+    <row r="63" spans="1:27" ht="19.149999999999999">
       <c r="A63" s="10">
         <v>7</v>
       </c>
@@ -9362,7 +9319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.2">
+    <row r="64" spans="1:27" ht="19.149999999999999">
       <c r="A64" s="10">
         <v>7</v>
       </c>
@@ -9431,7 +9388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.2">
+    <row r="65" spans="1:27" ht="19.149999999999999">
       <c r="A65" s="10">
         <v>7</v>
       </c>
@@ -9500,7 +9457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="19.2">
+    <row r="66" spans="1:27" ht="19.149999999999999">
       <c r="A66" s="10">
         <v>7</v>
       </c>
@@ -9569,7 +9526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="19.2">
+    <row r="67" spans="1:27" ht="19.149999999999999">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -9638,7 +9595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.2">
+    <row r="68" spans="1:27" ht="19.149999999999999">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -9707,7 +9664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.2">
+    <row r="69" spans="1:27" ht="19.149999999999999">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -9776,7 +9733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.2">
+    <row r="70" spans="1:27" ht="19.149999999999999">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -9845,7 +9802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.2">
+    <row r="71" spans="1:27" ht="19.149999999999999">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -9914,7 +9871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" s="7" customFormat="1" ht="19.2">
+    <row r="72" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J72" s="13"/>
       <c r="M72" s="5"/>
       <c r="N72" s="13"/>
@@ -9928,7 +9885,7 @@
       <c r="Z72" s="13"/>
       <c r="AA72" s="13"/>
     </row>
-    <row r="73" spans="1:27" ht="19.2">
+    <row r="73" spans="1:27" ht="19.149999999999999">
       <c r="A73" s="10">
         <v>8</v>
       </c>
@@ -9997,7 +9954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.2">
+    <row r="74" spans="1:27" ht="19.149999999999999">
       <c r="A74" s="10">
         <v>8</v>
       </c>
@@ -10066,7 +10023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.2">
+    <row r="75" spans="1:27" ht="19.149999999999999">
       <c r="A75" s="10">
         <v>8</v>
       </c>
@@ -10135,7 +10092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.2">
+    <row r="76" spans="1:27" ht="19.149999999999999">
       <c r="A76" s="10">
         <v>8</v>
       </c>
@@ -10204,7 +10161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.2">
+    <row r="77" spans="1:27" ht="19.149999999999999">
       <c r="A77" s="10">
         <v>8</v>
       </c>
@@ -10273,7 +10230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" ht="19.2">
+    <row r="78" spans="1:27" ht="19.149999999999999">
       <c r="A78" s="10">
         <v>8</v>
       </c>
@@ -10342,7 +10299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="19.2">
+    <row r="79" spans="1:27" ht="19.149999999999999">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -10411,7 +10368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.2">
+    <row r="80" spans="1:27" ht="19.149999999999999">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -10480,7 +10437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.2">
+    <row r="81" spans="1:27" ht="19.149999999999999">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -10549,7 +10506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.2">
+    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J82" s="13"/>
       <c r="M82" s="5"/>
       <c r="N82" s="13"/>
@@ -10563,7 +10520,7 @@
       <c r="Z82" s="13"/>
       <c r="AA82" s="13"/>
     </row>
-    <row r="83" spans="1:27" ht="19.2">
+    <row r="83" spans="1:27" ht="19.149999999999999">
       <c r="A83" s="10">
         <v>9</v>
       </c>
@@ -10632,7 +10589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.2">
+    <row r="84" spans="1:27" ht="19.149999999999999">
       <c r="A84" s="10">
         <v>9</v>
       </c>
@@ -10701,7 +10658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.2">
+    <row r="85" spans="1:27" ht="19.149999999999999">
       <c r="A85" s="10">
         <v>9</v>
       </c>
@@ -10770,7 +10727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.2">
+    <row r="86" spans="1:27" ht="19.149999999999999">
       <c r="A86" s="10">
         <v>9</v>
       </c>
@@ -10839,7 +10796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.2">
+    <row r="87" spans="1:27" ht="19.149999999999999">
       <c r="A87" s="10">
         <v>9</v>
       </c>
@@ -10908,7 +10865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.2">
+    <row r="88" spans="1:27" ht="19.149999999999999">
       <c r="A88" s="10">
         <v>9</v>
       </c>
@@ -10977,7 +10934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.2">
+    <row r="89" spans="1:27" ht="19.149999999999999">
       <c r="A89" s="10">
         <v>9</v>
       </c>
@@ -11046,7 +11003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" ht="19.2">
+    <row r="90" spans="1:27" ht="19.149999999999999">
       <c r="A90" s="10">
         <v>9</v>
       </c>
@@ -11115,7 +11072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:27" ht="19.2">
+    <row r="91" spans="1:27" ht="19.149999999999999">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -11184,7 +11141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" s="7" customFormat="1" ht="19.2">
+    <row r="92" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J92" s="13"/>
       <c r="M92" s="5"/>
       <c r="N92" s="13"/>
@@ -11198,7 +11155,7 @@
       <c r="Z92" s="13"/>
       <c r="AA92" s="13"/>
     </row>
-    <row r="93" spans="1:27" ht="19.2">
+    <row r="93" spans="1:27" ht="19.149999999999999">
       <c r="A93" s="10">
         <v>10</v>
       </c>
@@ -11267,7 +11224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.2">
+    <row r="94" spans="1:27" ht="19.149999999999999">
       <c r="A94" s="10">
         <v>10</v>
       </c>
@@ -11336,7 +11293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.2">
+    <row r="95" spans="1:27" ht="19.149999999999999">
       <c r="A95" s="10">
         <v>10</v>
       </c>
@@ -11405,7 +11362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.2">
+    <row r="96" spans="1:27" ht="19.149999999999999">
       <c r="A96" s="10">
         <v>10</v>
       </c>
@@ -11474,7 +11431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.2">
+    <row r="97" spans="1:27" ht="19.149999999999999">
       <c r="A97" s="10">
         <v>10</v>
       </c>
@@ -11543,7 +11500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.2">
+    <row r="98" spans="1:27" ht="19.149999999999999">
       <c r="A98" s="10">
         <v>10</v>
       </c>
@@ -11612,7 +11569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.2">
+    <row r="99" spans="1:27" ht="19.149999999999999">
       <c r="A99" s="10">
         <v>10</v>
       </c>
@@ -11681,7 +11638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.2">
+    <row r="100" spans="1:27" ht="19.149999999999999">
       <c r="A100" s="10">
         <v>10</v>
       </c>
@@ -11750,7 +11707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.2">
+    <row r="101" spans="1:27" ht="19.149999999999999">
       <c r="A101" s="10">
         <v>10</v>
       </c>
@@ -11819,7 +11776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:27" s="7" customFormat="1" ht="19.2">
+    <row r="102" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J102" s="13"/>
       <c r="M102" s="5"/>
       <c r="N102" s="13"/>
@@ -11833,7 +11790,7 @@
       <c r="Z102" s="13"/>
       <c r="AA102" s="13"/>
     </row>
-    <row r="103" spans="1:27" ht="38.4">
+    <row r="103" spans="1:27" ht="38.450000000000003">
       <c r="A103" s="1" t="s">
         <v>23</v>
       </c>
@@ -11902,7 +11859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.2">
+    <row r="104" spans="1:27" ht="19.149999999999999">
       <c r="A104" s="1" t="s">
         <v>23</v>
       </c>
@@ -11971,7 +11928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.2">
+    <row r="105" spans="1:27" ht="19.149999999999999">
       <c r="A105" s="1" t="s">
         <v>23</v>
       </c>
@@ -12040,7 +11997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.2">
+    <row r="106" spans="1:27" ht="19.149999999999999">
       <c r="A106" s="1" t="s">
         <v>23</v>
       </c>
@@ -12109,7 +12066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="38.4">
+    <row r="107" spans="1:27" ht="38.450000000000003">
       <c r="A107" s="1" t="s">
         <v>23</v>
       </c>
@@ -12178,7 +12135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="19.2">
+    <row r="108" spans="1:27" ht="19.149999999999999">
       <c r="A108" s="1" t="s">
         <v>23</v>
       </c>
@@ -12247,7 +12204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="38.4">
+    <row r="109" spans="1:27" ht="38.450000000000003">
       <c r="A109" s="1" t="s">
         <v>23</v>
       </c>
@@ -12316,7 +12273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="38.4">
+    <row r="110" spans="1:27" ht="38.450000000000003">
       <c r="A110" s="1" t="s">
         <v>23</v>
       </c>
@@ -12385,7 +12342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" s="7" customFormat="1" ht="19.2">
+    <row r="111" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J111" s="13"/>
       <c r="N111" s="13"/>
       <c r="O111" s="13"/>
@@ -12396,7 +12353,7 @@
       <c r="Z111" s="13"/>
       <c r="AA111" s="13"/>
     </row>
-    <row r="112" spans="1:27" ht="19.2">
+    <row r="112" spans="1:27" ht="19.149999999999999">
       <c r="A112" s="1"/>
       <c r="B112" s="9"/>
       <c r="C112" s="1"/>
@@ -12458,7 +12415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:27" ht="19.2">
+    <row r="113" spans="1:27" ht="19.149999999999999">
       <c r="A113" s="1"/>
       <c r="B113" s="9"/>
       <c r="C113" s="1"/>
@@ -12520,7 +12477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:27" ht="19.2">
+    <row r="114" spans="1:27" ht="19.149999999999999">
       <c r="A114" s="1"/>
       <c r="B114" s="9"/>
       <c r="C114" s="1"/>
@@ -12582,7 +12539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:27" ht="19.2">
+    <row r="115" spans="1:27" ht="19.149999999999999">
       <c r="A115" s="1"/>
       <c r="B115" s="9"/>
       <c r="C115" s="1"/>
@@ -12644,7 +12601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:27" ht="19.2">
+    <row r="116" spans="1:27" ht="19.149999999999999">
       <c r="A116" s="1"/>
       <c r="B116" s="9"/>
       <c r="C116" s="1"/>
@@ -12706,7 +12663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:27" ht="19.2">
+    <row r="117" spans="1:27" ht="19.149999999999999">
       <c r="A117" s="1"/>
       <c r="B117" s="9"/>
       <c r="C117" s="1"/>
@@ -12768,7 +12725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:27" ht="19.2">
+    <row r="118" spans="1:27" ht="19.149999999999999">
       <c r="A118" s="1"/>
       <c r="B118" s="9"/>
       <c r="C118" s="1"/>
@@ -12830,7 +12787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:27" ht="19.2">
+    <row r="119" spans="1:27" ht="19.149999999999999">
       <c r="A119" s="1"/>
       <c r="B119" s="9"/>
       <c r="C119" s="1"/>
@@ -12892,7 +12849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:27" ht="19.2">
+    <row r="120" spans="1:27" ht="19.149999999999999">
       <c r="A120" s="1"/>
       <c r="B120" s="9"/>
       <c r="C120" s="1"/>
@@ -12954,7 +12911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:27" ht="19.2">
+    <row r="121" spans="1:27" ht="19.149999999999999">
       <c r="A121" s="1"/>
       <c r="B121" s="9"/>
       <c r="C121" s="1"/>
@@ -13016,7 +12973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:27" ht="19.2">
+    <row r="122" spans="1:27" ht="19.149999999999999">
       <c r="A122" s="1"/>
       <c r="B122" s="9"/>
       <c r="C122" s="1"/>
@@ -13078,7 +13035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:27" ht="19.2">
+    <row r="123" spans="1:27" ht="19.149999999999999">
       <c r="A123" s="1"/>
       <c r="B123" s="9"/>
       <c r="C123" s="1"/>
@@ -13140,7 +13097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:27" ht="19.2">
+    <row r="124" spans="1:27" ht="19.149999999999999">
       <c r="A124" s="1"/>
       <c r="B124" s="9"/>
       <c r="C124" s="1"/>
@@ -13202,7 +13159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:27" ht="19.2">
+    <row r="125" spans="1:27" ht="19.149999999999999">
       <c r="A125" s="1"/>
       <c r="B125" s="9"/>
       <c r="C125" s="1"/>
@@ -13264,7 +13221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:27" ht="19.2">
+    <row r="126" spans="1:27" ht="19.149999999999999">
       <c r="A126" s="1"/>
       <c r="B126" s="9"/>
       <c r="C126" s="1"/>
@@ -13326,14 +13283,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:27" ht="19.2">
-      <c r="A127" s="32"/>
-      <c r="B127" s="33"/>
-      <c r="C127" s="32"/>
+    <row r="127" spans="1:27" ht="19.149999999999999">
+      <c r="A127" s="29"/>
+      <c r="B127" s="30"/>
+      <c r="C127" s="29"/>
       <c r="D127" s="5"/>
-      <c r="E127" s="34"/>
-      <c r="F127" s="32"/>
-      <c r="G127" s="34"/>
+      <c r="E127" s="31"/>
+      <c r="F127" s="29"/>
+      <c r="G127" s="31"/>
       <c r="H127" s="5">
         <f t="shared" si="22"/>
         <v>0</v>
@@ -13346,9 +13303,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K127" s="34"/>
-      <c r="L127" s="32"/>
-      <c r="M127" s="34"/>
+      <c r="K127" s="31"/>
+      <c r="L127" s="29"/>
+      <c r="M127" s="31"/>
       <c r="N127" s="5">
         <f t="shared" ref="N127" si="24">IF((J127-K127)&lt;0,0,(J127-K127))</f>
         <v>0</v>
@@ -13358,9 +13315,9 @@
         <v>0</v>
       </c>
       <c r="P127" s="5"/>
-      <c r="Q127" s="34"/>
-      <c r="R127" s="32"/>
-      <c r="S127" s="34"/>
+      <c r="Q127" s="31"/>
+      <c r="R127" s="29"/>
+      <c r="S127" s="31"/>
       <c r="T127" s="5">
         <f t="shared" si="18"/>
         <v>0</v>
@@ -13373,9 +13330,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W127" s="34"/>
-      <c r="X127" s="32"/>
-      <c r="Y127" s="34"/>
+      <c r="W127" s="31"/>
+      <c r="X127" s="29"/>
+      <c r="Y127" s="31"/>
       <c r="Z127" s="5">
         <f t="shared" si="20"/>
         <v>0</v>
@@ -13383,186 +13340,6 @@
       <c r="AA127" s="5">
         <f t="shared" si="21"/>
         <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
       </c>
     </row>
   </sheetData>
@@ -13582,8 +13359,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X112:X127 F5:F12 F14:F21 F23:F31 F33:F41 F43:F51 F53:F61 F63:F71 F73:F81 F83:F91 F93:F101 F103:F110 F112:F127 L5:L12 L14:L21 L23:L31 L33:L41 L43:L51 L53:L61 L63:L71 L73:L81 L83:L91 L93:L101 L103:L110 L112:L127 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12 X5:X12 X14:X21 X23:X31 X33:X41 X43:X51 X53:X61 X63:X71 X73:X81 X83:X91 X93:X101 X103:X110" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025 ,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
@@ -13601,154 +13378,153 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <dimension ref="A1:AB140"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="9.3984375" customWidth="1"/>
-    <col min="2" max="2" width="27.8984375" style="49" customWidth="1"/>
-    <col min="3" max="3" width="17.19921875" customWidth="1"/>
-    <col min="4" max="4" width="16.3984375" customWidth="1"/>
-    <col min="5" max="5" width="23.19921875" customWidth="1"/>
-    <col min="6" max="6" width="24.8984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.59765625" customWidth="1"/>
-    <col min="8" max="9" width="20.8984375" customWidth="1"/>
-    <col min="10" max="10" width="13.69921875" customWidth="1"/>
-    <col min="11" max="11" width="24.3984375" customWidth="1"/>
-    <col min="12" max="12" width="18.19921875" customWidth="1"/>
-    <col min="13" max="13" width="20.796875" customWidth="1"/>
-    <col min="14" max="15" width="20.8984375" customWidth="1"/>
-    <col min="16" max="16" width="21.59765625" customWidth="1"/>
-    <col min="17" max="17" width="29.19921875" customWidth="1"/>
-    <col min="18" max="18" width="25.796875" customWidth="1"/>
-    <col min="19" max="19" width="32.8984375" customWidth="1"/>
-    <col min="20" max="21" width="20.8984375" customWidth="1"/>
-    <col min="22" max="22" width="16.19921875" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" customWidth="1"/>
+    <col min="2" max="2" width="27.85546875" customWidth="1"/>
+    <col min="3" max="3" width="17.140625" customWidth="1"/>
+    <col min="4" max="4" width="16.42578125" customWidth="1"/>
+    <col min="5" max="5" width="23.140625" customWidth="1"/>
+    <col min="6" max="6" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5703125" customWidth="1"/>
+    <col min="8" max="9" width="20.85546875" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" customWidth="1"/>
+    <col min="11" max="11" width="24.42578125" customWidth="1"/>
+    <col min="12" max="12" width="18.140625" customWidth="1"/>
+    <col min="13" max="15" width="20.85546875" customWidth="1"/>
+    <col min="16" max="16" width="21.5703125" customWidth="1"/>
+    <col min="17" max="17" width="29.140625" customWidth="1"/>
+    <col min="18" max="18" width="25.85546875" customWidth="1"/>
+    <col min="19" max="19" width="32.85546875" customWidth="1"/>
+    <col min="20" max="21" width="20.85546875" customWidth="1"/>
+    <col min="22" max="22" width="16.140625" customWidth="1"/>
     <col min="23" max="23" width="25" customWidth="1"/>
-    <col min="24" max="24" width="15.296875" customWidth="1"/>
-    <col min="25" max="25" width="20.796875" customWidth="1"/>
-    <col min="26" max="26" width="14.796875" customWidth="1"/>
-    <col min="27" max="27" width="15.19921875" customWidth="1"/>
+    <col min="24" max="24" width="15.28515625" customWidth="1"/>
+    <col min="25" max="25" width="20.85546875" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" customWidth="1"/>
+    <col min="27" max="27" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="31" customFormat="1" ht="34.200000000000003" customHeight="1">
-      <c r="B1" s="46"/>
-      <c r="D1" s="38" t="s">
+    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
+      <c r="B1" s="35"/>
+      <c r="D1" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="39" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
-      <c r="N1" s="39"/>
-      <c r="O1" s="39"/>
-      <c r="P1" s="40" t="s">
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="Q1" s="40"/>
-      <c r="R1" s="40"/>
-      <c r="S1" s="40"/>
-      <c r="T1" s="40"/>
-      <c r="U1" s="40"/>
-      <c r="V1" s="41" t="s">
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="44"/>
+      <c r="V1" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="W1" s="41"/>
-      <c r="X1" s="41"/>
-      <c r="Y1" s="41"/>
-      <c r="Z1" s="41"/>
-      <c r="AA1" s="41"/>
+      <c r="W1" s="45"/>
+      <c r="X1" s="45"/>
+      <c r="Y1" s="45"/>
+      <c r="Z1" s="45"/>
+      <c r="AA1" s="45"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="36" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="16" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="G2" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="H2" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="H2" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="I2" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="J2" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="K2" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="I2" s="26" t="s">
+      <c r="L2" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="K2" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="L2" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="M2" s="24" t="s">
+      <c r="M2" s="40" t="s">
+        <v>71</v>
+      </c>
+      <c r="N2" s="40" t="s">
         <v>72</v>
-      </c>
-      <c r="N2" s="24" t="s">
-        <v>71</v>
       </c>
       <c r="O2" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="P2" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q2" s="26" t="s">
+      <c r="P2" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q2" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="R2" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="S2" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="T2" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="U2" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="V2" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="W2" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="X2" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y2" s="41" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z2" s="41" t="s">
         <v>84</v>
       </c>
-      <c r="R2" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="S2" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="T2" s="25" t="s">
-        <v>75</v>
-      </c>
-      <c r="U2" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="V2" s="28" t="s">
-        <v>56</v>
-      </c>
-      <c r="W2" s="28" t="s">
-        <v>81</v>
-      </c>
-      <c r="X2" s="29" t="s">
-        <v>77</v>
-      </c>
-      <c r="Y2" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="Z2" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="AA2" s="28" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="19.2">
+      <c r="AA2" s="26" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" ht="19.149999999999999">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -13817,7 +13593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="19.2">
+    <row r="4" spans="1:27" ht="19.149999999999999">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -13886,7 +13662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="19.2">
+    <row r="5" spans="1:27" ht="19.149999999999999">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -13955,7 +13731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.2">
+    <row r="6" spans="1:27" ht="19.149999999999999">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -14024,7 +13800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.2">
+    <row r="7" spans="1:27" ht="19.149999999999999">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -14093,26 +13869,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.2">
-      <c r="A8" s="35">
+    <row r="8" spans="1:27" ht="19.149999999999999">
+      <c r="A8" s="1">
         <v>1</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="35"/>
-      <c r="D8" s="37">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="37"/>
-      <c r="F8" s="35"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="5">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="F8" s="1"/>
       <c r="G8" s="5"/>
-      <c r="H8" s="37">
+      <c r="H8" s="5">
         <f>IF((D8-E8)&lt;0,0,(D8-E8))</f>
         <v>0</v>
       </c>
-      <c r="I8" s="37">
+      <c r="I8" s="5">
         <f>IF((E8-D8)&lt;0,0,(E8-D8))</f>
         <v>0</v>
       </c>
@@ -14120,8 +13896,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K8" s="37"/>
-      <c r="L8" s="35"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="1"/>
       <c r="M8" s="5"/>
       <c r="N8" s="5">
         <f t="shared" si="2"/>
@@ -14135,8 +13911,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q8" s="37"/>
-      <c r="R8" s="35"/>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="1"/>
       <c r="S8" s="5"/>
       <c r="T8" s="5">
         <f t="shared" si="4"/>
@@ -14150,8 +13926,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W8" s="37"/>
-      <c r="X8" s="35"/>
+      <c r="W8" s="5"/>
+      <c r="X8" s="1"/>
       <c r="Y8" s="5"/>
       <c r="Z8" s="5">
         <f t="shared" si="6"/>
@@ -14162,26 +13938,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.2">
-      <c r="A9" s="35">
+    <row r="9" spans="1:27" ht="19.149999999999999">
+      <c r="A9" s="1">
         <v>1</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="35"/>
-      <c r="D9" s="37">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E9" s="37"/>
-      <c r="F9" s="35"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="5">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="5"/>
+      <c r="F9" s="1"/>
       <c r="G9" s="5"/>
-      <c r="H9" s="37">
+      <c r="H9" s="5">
         <f>IF((D9-E9)&lt;0,0,(D9-E9))</f>
         <v>0</v>
       </c>
-      <c r="I9" s="37">
+      <c r="I9" s="5">
         <f>IF((E9-D9)&lt;0,0,(E9-D9))</f>
         <v>0</v>
       </c>
@@ -14189,8 +13965,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K9" s="37"/>
-      <c r="L9" s="35"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="1"/>
       <c r="M9" s="5"/>
       <c r="N9" s="5">
         <f t="shared" si="2"/>
@@ -14204,8 +13980,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q9" s="37"/>
-      <c r="R9" s="35"/>
+      <c r="Q9" s="5"/>
+      <c r="R9" s="1"/>
       <c r="S9" s="5"/>
       <c r="T9" s="5">
         <f t="shared" si="4"/>
@@ -14219,8 +13995,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W9" s="37"/>
-      <c r="X9" s="35"/>
+      <c r="W9" s="5"/>
+      <c r="X9" s="1"/>
       <c r="Y9" s="5"/>
       <c r="Z9" s="5">
         <f t="shared" si="6"/>
@@ -14231,26 +14007,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.2">
-      <c r="A10" s="35">
+    <row r="10" spans="1:27" ht="19.149999999999999">
+      <c r="A10" s="1">
         <v>1</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="35"/>
-      <c r="D10" s="37">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="37"/>
-      <c r="F10" s="35"/>
+        <v>61</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="5">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="5"/>
+      <c r="F10" s="1"/>
       <c r="G10" s="5"/>
-      <c r="H10" s="37">
+      <c r="H10" s="5">
         <f>IF((D10-E10)&lt;0,0,(D10-E10))</f>
         <v>0</v>
       </c>
-      <c r="I10" s="37">
+      <c r="I10" s="5">
         <f>IF((E10-D10)&lt;0,0,(E10-D10))</f>
         <v>0</v>
       </c>
@@ -14258,8 +14034,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K10" s="37"/>
-      <c r="L10" s="35"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="1"/>
       <c r="M10" s="5"/>
       <c r="N10" s="5">
         <f t="shared" si="2"/>
@@ -14273,8 +14049,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q10" s="37"/>
-      <c r="R10" s="35"/>
+      <c r="Q10" s="5"/>
+      <c r="R10" s="1"/>
       <c r="S10" s="5"/>
       <c r="T10" s="5">
         <f t="shared" si="4"/>
@@ -14288,8 +14064,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W10" s="37"/>
-      <c r="X10" s="35"/>
+      <c r="W10" s="5"/>
+      <c r="X10" s="1"/>
       <c r="Y10" s="5"/>
       <c r="Z10" s="5">
         <f t="shared" si="6"/>
@@ -14300,10 +14076,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" s="7" customFormat="1">
-      <c r="B11" s="48"/>
-    </row>
-    <row r="12" spans="1:27" ht="19.2">
+    <row r="11" spans="1:27" s="7" customFormat="1"/>
+    <row r="12" spans="1:27" ht="19.149999999999999">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -14372,7 +14146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="19.2">
+    <row r="13" spans="1:27" ht="19.149999999999999">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -14441,7 +14215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="19.2">
+    <row r="14" spans="1:27" ht="19.149999999999999">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -14510,7 +14284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.2">
+    <row r="15" spans="1:27" ht="19.149999999999999">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -14579,7 +14353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.2">
+    <row r="16" spans="1:27" ht="19.149999999999999">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -14648,26 +14422,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.2">
-      <c r="A17" s="35">
+    <row r="17" spans="1:27" ht="19.149999999999999">
+      <c r="A17" s="1">
         <v>2</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="35"/>
-      <c r="D17" s="37">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="37"/>
-      <c r="F17" s="35"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="5">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="5"/>
+      <c r="F17" s="1"/>
       <c r="G17" s="5"/>
-      <c r="H17" s="37">
+      <c r="H17" s="5">
         <f>IF((D17-E17)&lt;0,0,(D17-E17))</f>
         <v>0</v>
       </c>
-      <c r="I17" s="37">
+      <c r="I17" s="5">
         <f>IF((E17-D17)&lt;0,0,(E17-D17))</f>
         <v>0</v>
       </c>
@@ -14675,8 +14449,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K17" s="37"/>
-      <c r="L17" s="35"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="1"/>
       <c r="M17" s="5"/>
       <c r="N17" s="5">
         <f t="shared" si="2"/>
@@ -14690,8 +14464,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q17" s="37"/>
-      <c r="R17" s="35"/>
+      <c r="Q17" s="5"/>
+      <c r="R17" s="1"/>
       <c r="S17" s="5"/>
       <c r="T17" s="5">
         <f t="shared" si="4"/>
@@ -14705,8 +14479,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W17" s="37"/>
-      <c r="X17" s="35"/>
+      <c r="W17" s="5"/>
+      <c r="X17" s="1"/>
       <c r="Y17" s="5"/>
       <c r="Z17" s="5">
         <f t="shared" si="6"/>
@@ -14717,26 +14491,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.2">
-      <c r="A18" s="35">
+    <row r="18" spans="1:27" ht="19.149999999999999">
+      <c r="A18" s="1">
         <v>2</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="35"/>
-      <c r="D18" s="37">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E18" s="37"/>
-      <c r="F18" s="35"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="5">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="5"/>
+      <c r="F18" s="1"/>
       <c r="G18" s="5"/>
-      <c r="H18" s="37">
+      <c r="H18" s="5">
         <f>IF((D18-E18)&lt;0,0,(D18-E18))</f>
         <v>0</v>
       </c>
-      <c r="I18" s="37">
+      <c r="I18" s="5">
         <f>IF((E18-D18)&lt;0,0,(E18-D18))</f>
         <v>0</v>
       </c>
@@ -14744,8 +14518,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K18" s="37"/>
-      <c r="L18" s="35"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="1"/>
       <c r="M18" s="5"/>
       <c r="N18" s="5">
         <f t="shared" si="2"/>
@@ -14759,8 +14533,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q18" s="37"/>
-      <c r="R18" s="35"/>
+      <c r="Q18" s="5"/>
+      <c r="R18" s="1"/>
       <c r="S18" s="5"/>
       <c r="T18" s="5">
         <f t="shared" si="4"/>
@@ -14774,8 +14548,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W18" s="37"/>
-      <c r="X18" s="35"/>
+      <c r="W18" s="5"/>
+      <c r="X18" s="1"/>
       <c r="Y18" s="5"/>
       <c r="Z18" s="5">
         <f t="shared" si="6"/>
@@ -14786,26 +14560,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.2">
-      <c r="A19" s="35">
+    <row r="19" spans="1:27" ht="19.149999999999999">
+      <c r="A19" s="1">
         <v>2</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C19" s="35"/>
-      <c r="D19" s="37">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E19" s="37"/>
-      <c r="F19" s="35"/>
+        <v>61</v>
+      </c>
+      <c r="C19" s="1"/>
+      <c r="D19" s="5">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="5"/>
+      <c r="F19" s="1"/>
       <c r="G19" s="5"/>
-      <c r="H19" s="37">
+      <c r="H19" s="5">
         <f>IF((D19-E19)&lt;0,0,(D19-E19))</f>
         <v>0</v>
       </c>
-      <c r="I19" s="37">
+      <c r="I19" s="5">
         <f>IF((E19-D19)&lt;0,0,(E19-D19))</f>
         <v>0</v>
       </c>
@@ -14813,8 +14587,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K19" s="37"/>
-      <c r="L19" s="35"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="1"/>
       <c r="M19" s="5"/>
       <c r="N19" s="5">
         <f t="shared" si="2"/>
@@ -14828,8 +14602,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q19" s="37"/>
-      <c r="R19" s="35"/>
+      <c r="Q19" s="5"/>
+      <c r="R19" s="1"/>
       <c r="S19" s="5"/>
       <c r="T19" s="5">
         <f t="shared" si="4"/>
@@ -14843,8 +14617,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W19" s="37"/>
-      <c r="X19" s="35"/>
+      <c r="W19" s="5"/>
+      <c r="X19" s="1"/>
       <c r="Y19" s="5"/>
       <c r="Z19" s="5">
         <f t="shared" si="6"/>
@@ -14855,10 +14629,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" s="7" customFormat="1">
-      <c r="B20" s="48"/>
-    </row>
-    <row r="21" spans="1:27" ht="19.2">
+    <row r="20" spans="1:27" s="7" customFormat="1"/>
+    <row r="21" spans="1:27" ht="19.149999999999999">
       <c r="A21" s="1">
         <v>3</v>
       </c>
@@ -14927,7 +14699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="19.2">
+    <row r="22" spans="1:27" ht="19.149999999999999">
       <c r="A22" s="1">
         <v>3</v>
       </c>
@@ -14996,7 +14768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="19.2">
+    <row r="23" spans="1:27" ht="19.149999999999999">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -15065,7 +14837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.2">
+    <row r="24" spans="1:27" ht="19.149999999999999">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -15134,7 +14906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.2">
+    <row r="25" spans="1:27" ht="19.149999999999999">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -15203,7 +14975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.2">
+    <row r="26" spans="1:27" ht="19.149999999999999">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -15272,26 +15044,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.2">
-      <c r="A27" s="35">
+    <row r="27" spans="1:27" ht="19.149999999999999">
+      <c r="A27" s="1">
         <v>3</v>
       </c>
       <c r="B27" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C27" s="35"/>
-      <c r="D27" s="37">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E27" s="37"/>
-      <c r="F27" s="35"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="5">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="5"/>
+      <c r="F27" s="1"/>
       <c r="G27" s="5"/>
-      <c r="H27" s="37">
+      <c r="H27" s="5">
         <f>IF((D27-E27)&lt;0,0,(D27-E27))</f>
         <v>0</v>
       </c>
-      <c r="I27" s="37">
+      <c r="I27" s="5">
         <f>IF((E27-D27)&lt;0,0,(E27-D27))</f>
         <v>0</v>
       </c>
@@ -15299,8 +15071,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K27" s="37"/>
-      <c r="L27" s="35"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="1"/>
       <c r="M27" s="5"/>
       <c r="N27" s="5">
         <f t="shared" si="2"/>
@@ -15314,8 +15086,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q27" s="37"/>
-      <c r="R27" s="35"/>
+      <c r="Q27" s="5"/>
+      <c r="R27" s="1"/>
       <c r="S27" s="5"/>
       <c r="T27" s="5">
         <f t="shared" si="4"/>
@@ -15329,8 +15101,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W27" s="37"/>
-      <c r="X27" s="35"/>
+      <c r="W27" s="5"/>
+      <c r="X27" s="1"/>
       <c r="Y27" s="5"/>
       <c r="Z27" s="5">
         <f t="shared" si="6"/>
@@ -15341,26 +15113,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.2">
-      <c r="A28" s="35">
+    <row r="28" spans="1:27" ht="19.149999999999999">
+      <c r="A28" s="1">
         <v>3</v>
       </c>
       <c r="B28" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C28" s="35"/>
-      <c r="D28" s="37">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E28" s="37"/>
-      <c r="F28" s="35"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="5">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="5"/>
+      <c r="F28" s="1"/>
       <c r="G28" s="5"/>
-      <c r="H28" s="37">
+      <c r="H28" s="5">
         <f>IF((D28-E28)&lt;0,0,(D28-E28))</f>
         <v>0</v>
       </c>
-      <c r="I28" s="37">
+      <c r="I28" s="5">
         <f>IF((E28-D28)&lt;0,0,(E28-D28))</f>
         <v>0</v>
       </c>
@@ -15368,8 +15140,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K28" s="37"/>
-      <c r="L28" s="35"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="1"/>
       <c r="M28" s="5"/>
       <c r="N28" s="5">
         <f t="shared" si="2"/>
@@ -15383,8 +15155,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q28" s="37"/>
-      <c r="R28" s="35"/>
+      <c r="Q28" s="5"/>
+      <c r="R28" s="1"/>
       <c r="S28" s="5"/>
       <c r="T28" s="5">
         <f t="shared" si="4"/>
@@ -15398,8 +15170,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W28" s="37"/>
-      <c r="X28" s="35"/>
+      <c r="W28" s="5"/>
+      <c r="X28" s="1"/>
       <c r="Y28" s="5"/>
       <c r="Z28" s="5">
         <f t="shared" si="6"/>
@@ -15410,26 +15182,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.2">
-      <c r="A29" s="35">
+    <row r="29" spans="1:27" ht="19.149999999999999">
+      <c r="A29" s="1">
         <v>3</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C29" s="35"/>
-      <c r="D29" s="37">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E29" s="37"/>
-      <c r="F29" s="35"/>
+        <v>61</v>
+      </c>
+      <c r="C29" s="1"/>
+      <c r="D29" s="5">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="5"/>
+      <c r="F29" s="1"/>
       <c r="G29" s="5"/>
-      <c r="H29" s="37">
+      <c r="H29" s="5">
         <f>IF((D29-E29)&lt;0,0,(D29-E29))</f>
         <v>0</v>
       </c>
-      <c r="I29" s="37">
+      <c r="I29" s="5">
         <f>IF((E29-D29)&lt;0,0,(E29-D29))</f>
         <v>0</v>
       </c>
@@ -15437,8 +15209,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K29" s="37"/>
-      <c r="L29" s="35"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="1"/>
       <c r="M29" s="5"/>
       <c r="N29" s="5">
         <f t="shared" si="2"/>
@@ -15452,8 +15224,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q29" s="37"/>
-      <c r="R29" s="35"/>
+      <c r="Q29" s="5"/>
+      <c r="R29" s="1"/>
       <c r="S29" s="5"/>
       <c r="T29" s="5">
         <f t="shared" si="4"/>
@@ -15467,8 +15239,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W29" s="37"/>
-      <c r="X29" s="35"/>
+      <c r="W29" s="5"/>
+      <c r="X29" s="1"/>
       <c r="Y29" s="5"/>
       <c r="Z29" s="5">
         <f t="shared" si="6"/>
@@ -15479,10 +15251,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" s="7" customFormat="1">
-      <c r="B30" s="48"/>
-    </row>
-    <row r="31" spans="1:27" ht="19.2">
+    <row r="30" spans="1:27" s="7" customFormat="1"/>
+    <row r="31" spans="1:27" ht="19.149999999999999">
       <c r="A31" s="1">
         <v>4</v>
       </c>
@@ -15551,7 +15321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="19.2">
+    <row r="32" spans="1:27" ht="19.149999999999999">
       <c r="A32" s="1">
         <v>4</v>
       </c>
@@ -15620,7 +15390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="19.2">
+    <row r="33" spans="1:27" ht="19.149999999999999">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -15689,7 +15459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.2">
+    <row r="34" spans="1:27" ht="19.149999999999999">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -15758,7 +15528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.2">
+    <row r="35" spans="1:27" ht="19.149999999999999">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -15827,7 +15597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.2">
+    <row r="36" spans="1:27" ht="19.149999999999999">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -15896,8 +15666,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.2">
-      <c r="A37" s="50">
+    <row r="37" spans="1:27" ht="19.149999999999999">
+      <c r="A37" s="37">
         <v>4</v>
       </c>
       <c r="B37" s="9" t="s">
@@ -15911,11 +15681,11 @@
       <c r="E37" s="5"/>
       <c r="F37" s="1"/>
       <c r="G37" s="5"/>
-      <c r="H37" s="51">
+      <c r="H37" s="5">
         <f>IF((D37-E37)&lt;0,0,(D37-E37))</f>
         <v>0</v>
       </c>
-      <c r="I37" s="51">
+      <c r="I37" s="5">
         <f>IF((E37-D37)&lt;0,0,(E37-D37))</f>
         <v>0</v>
       </c>
@@ -15965,12 +15735,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.2">
+    <row r="38" spans="1:27" ht="19.149999999999999">
       <c r="A38" s="1">
         <v>4</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="5">
@@ -16034,7 +15804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.2">
+    <row r="39" spans="1:27" ht="19.149999999999999">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -16103,12 +15873,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.2">
-      <c r="A40" s="50">
+    <row r="40" spans="1:27" ht="19.149999999999999">
+      <c r="A40" s="37">
         <v>4</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="5">
@@ -16118,11 +15888,11 @@
       <c r="E40" s="5"/>
       <c r="F40" s="1"/>
       <c r="G40" s="5"/>
-      <c r="H40" s="51">
+      <c r="H40" s="5">
         <f>IF((D40-E40)&lt;0,0,(D40-E40))</f>
         <v>0</v>
       </c>
-      <c r="I40" s="51">
+      <c r="I40" s="5">
         <f>IF((E40-D40)&lt;0,0,(E40-D40))</f>
         <v>0</v>
       </c>
@@ -16172,12 +15942,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.2">
+    <row r="41" spans="1:27" ht="19.149999999999999">
       <c r="A41" s="1">
         <v>4</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="5">
@@ -16241,10 +16011,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1">
-      <c r="B42" s="48"/>
-    </row>
-    <row r="43" spans="1:27" ht="19.2">
+    <row r="42" spans="1:27" s="7" customFormat="1"/>
+    <row r="43" spans="1:27" ht="19.149999999999999">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -16313,7 +16081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.2">
+    <row r="44" spans="1:27" ht="19.149999999999999">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -16382,7 +16150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.2">
+    <row r="45" spans="1:27" ht="19.149999999999999">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -16451,7 +16219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.2">
+    <row r="46" spans="1:27" ht="19.149999999999999">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -16520,7 +16288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.2">
+    <row r="47" spans="1:27" ht="19.149999999999999">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -16589,7 +16357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.2">
+    <row r="48" spans="1:27" ht="19.149999999999999">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -16658,8 +16426,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.2">
-      <c r="A49" s="50">
+    <row r="49" spans="1:27" ht="19.149999999999999">
+      <c r="A49" s="37">
         <v>5</v>
       </c>
       <c r="B49" s="9" t="s">
@@ -16673,11 +16441,11 @@
       <c r="E49" s="5"/>
       <c r="F49" s="1"/>
       <c r="G49" s="5"/>
-      <c r="H49" s="51">
+      <c r="H49" s="5">
         <f>IF((D49-E49)&lt;0,0,(D49-E49))</f>
         <v>0</v>
       </c>
-      <c r="I49" s="51">
+      <c r="I49" s="5">
         <f>IF((E49-D49)&lt;0,0,(E49-D49))</f>
         <v>0</v>
       </c>
@@ -16727,12 +16495,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.2">
+    <row r="50" spans="1:27" ht="19.149999999999999">
       <c r="A50" s="1">
         <v>5</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="5">
@@ -16796,7 +16564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.2">
+    <row r="51" spans="1:27" ht="19.149999999999999">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -16865,12 +16633,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="19.2">
-      <c r="A52" s="50">
+    <row r="52" spans="1:27" ht="19.149999999999999">
+      <c r="A52" s="37">
         <v>5</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C52" s="5"/>
       <c r="D52" s="5">
@@ -16880,11 +16648,11 @@
       <c r="E52" s="5"/>
       <c r="F52" s="1"/>
       <c r="G52" s="5"/>
-      <c r="H52" s="51">
+      <c r="H52" s="5">
         <f>IF((D52-E52)&lt;0,0,(D52-E52))</f>
         <v>0</v>
       </c>
-      <c r="I52" s="51">
+      <c r="I52" s="5">
         <f>IF((E52-D52)&lt;0,0,(E52-D52))</f>
         <v>0</v>
       </c>
@@ -16934,12 +16702,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="19.2">
+    <row r="53" spans="1:27" ht="19.149999999999999">
       <c r="A53" s="1">
         <v>5</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="5">
@@ -17003,10 +16771,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" s="7" customFormat="1">
-      <c r="B54" s="48"/>
-    </row>
-    <row r="55" spans="1:27" ht="19.2">
+    <row r="54" spans="1:27" s="7" customFormat="1"/>
+    <row r="55" spans="1:27" ht="19.149999999999999">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -17075,7 +16841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.2">
+    <row r="56" spans="1:27" ht="19.149999999999999">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -17144,7 +16910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.2">
+    <row r="57" spans="1:27" ht="19.149999999999999">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -17213,7 +16979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.2">
+    <row r="58" spans="1:27" ht="19.149999999999999">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -17282,7 +17048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.2">
+    <row r="59" spans="1:27" ht="19.149999999999999">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -17351,7 +17117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.2">
+    <row r="60" spans="1:27" ht="19.149999999999999">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -17420,8 +17186,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.2">
-      <c r="A61" s="50">
+    <row r="61" spans="1:27" ht="19.149999999999999">
+      <c r="A61" s="37">
         <v>6</v>
       </c>
       <c r="B61" s="9" t="s">
@@ -17435,11 +17201,11 @@
       <c r="E61" s="5"/>
       <c r="F61" s="1"/>
       <c r="G61" s="5"/>
-      <c r="H61" s="51">
+      <c r="H61" s="5">
         <f>IF((D61-E61)&lt;0,0,(D61-E61))</f>
         <v>0</v>
       </c>
-      <c r="I61" s="51">
+      <c r="I61" s="5">
         <f>IF((E61-D61)&lt;0,0,(E61-D61))</f>
         <v>0</v>
       </c>
@@ -17489,12 +17255,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="19.2">
+    <row r="62" spans="1:27" ht="19.149999999999999">
       <c r="A62" s="1">
         <v>6</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C62" s="1"/>
       <c r="D62" s="5">
@@ -17558,7 +17324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="19.2">
+    <row r="63" spans="1:27" ht="19.149999999999999">
       <c r="A63" s="1">
         <v>6</v>
       </c>
@@ -17627,12 +17393,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.2">
-      <c r="A64" s="50">
+    <row r="64" spans="1:27" ht="19.149999999999999">
+      <c r="A64" s="37">
         <v>6</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C64" s="5"/>
       <c r="D64" s="5">
@@ -17642,11 +17408,11 @@
       <c r="E64" s="5"/>
       <c r="F64" s="1"/>
       <c r="G64" s="5"/>
-      <c r="H64" s="51">
+      <c r="H64" s="5">
         <f>IF((D64-E64)&lt;0,0,(D64-E64))</f>
         <v>0</v>
       </c>
-      <c r="I64" s="51">
+      <c r="I64" s="5">
         <f>IF((E64-D64)&lt;0,0,(E64-D64))</f>
         <v>0</v>
       </c>
@@ -17696,12 +17462,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.2">
+    <row r="65" spans="1:27" ht="19.149999999999999">
       <c r="A65" s="1">
         <v>6</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C65" s="1"/>
       <c r="D65" s="5">
@@ -17765,10 +17531,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" s="7" customFormat="1">
-      <c r="B66" s="48"/>
-    </row>
-    <row r="67" spans="1:27" ht="19.2">
+    <row r="66" spans="1:27" s="7" customFormat="1"/>
+    <row r="67" spans="1:27" ht="19.149999999999999">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -17837,7 +17601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.2">
+    <row r="68" spans="1:27" ht="19.149999999999999">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -17906,7 +17670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.2">
+    <row r="69" spans="1:27" ht="19.149999999999999">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -17975,7 +17739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.2">
+    <row r="70" spans="1:27" ht="19.149999999999999">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -18044,7 +17808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.2">
+    <row r="71" spans="1:27" ht="19.149999999999999">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -18113,7 +17877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="19.2">
+    <row r="72" spans="1:27" ht="19.149999999999999">
       <c r="A72" s="10">
         <v>7</v>
       </c>
@@ -18182,8 +17946,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="19.2">
-      <c r="A73" s="52">
+    <row r="73" spans="1:27" ht="19.149999999999999">
+      <c r="A73" s="38">
         <v>7</v>
       </c>
       <c r="B73" s="11" t="s">
@@ -18197,11 +17961,11 @@
       <c r="E73" s="12"/>
       <c r="F73" s="10"/>
       <c r="G73" s="12"/>
-      <c r="H73" s="54">
+      <c r="H73" s="12">
         <f>IF((D73-E73)&lt;0,0,(D73-E73))</f>
         <v>0</v>
       </c>
-      <c r="I73" s="54">
+      <c r="I73" s="12">
         <f>IF((E73-D73)&lt;0,0,(E73-D73))</f>
         <v>0</v>
       </c>
@@ -18251,12 +18015,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.2">
+    <row r="74" spans="1:27" ht="19.149999999999999">
       <c r="A74" s="10">
         <v>7</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C74" s="10"/>
       <c r="D74" s="12">
@@ -18320,7 +18084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.2">
+    <row r="75" spans="1:27" ht="19.149999999999999">
       <c r="A75" s="10">
         <v>7</v>
       </c>
@@ -18389,12 +18153,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.2">
-      <c r="A76" s="52">
+    <row r="76" spans="1:27" ht="19.149999999999999">
+      <c r="A76" s="38">
         <v>7</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C76" s="12"/>
       <c r="D76" s="12">
@@ -18404,11 +18168,11 @@
       <c r="E76" s="12"/>
       <c r="F76" s="10"/>
       <c r="G76" s="12"/>
-      <c r="H76" s="54">
+      <c r="H76" s="12">
         <f>IF((D76-E76)&lt;0,0,(D76-E76))</f>
         <v>0</v>
       </c>
-      <c r="I76" s="54">
+      <c r="I76" s="12">
         <f>IF((E76-D76)&lt;0,0,(E76-D76))</f>
         <v>0</v>
       </c>
@@ -18458,12 +18222,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.2">
+    <row r="77" spans="1:27" ht="19.149999999999999">
       <c r="A77" s="10">
         <v>7</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="12">
@@ -18527,10 +18291,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" s="7" customFormat="1">
-      <c r="B78" s="48"/>
-    </row>
-    <row r="79" spans="1:27" ht="19.2">
+    <row r="78" spans="1:27" s="7" customFormat="1"/>
+    <row r="79" spans="1:27" ht="19.149999999999999">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -18599,7 +18361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.2">
+    <row r="80" spans="1:27" ht="19.149999999999999">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -18668,7 +18430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.2">
+    <row r="81" spans="1:27" ht="19.149999999999999">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -18737,7 +18499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="19.2">
+    <row r="82" spans="1:27" ht="19.149999999999999">
       <c r="A82" s="10">
         <v>8</v>
       </c>
@@ -18806,7 +18568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="19.2">
+    <row r="83" spans="1:27" ht="19.149999999999999">
       <c r="A83" s="10">
         <v>8</v>
       </c>
@@ -18875,7 +18637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.2">
+    <row r="84" spans="1:27" ht="19.149999999999999">
       <c r="A84" s="10">
         <v>8</v>
       </c>
@@ -18944,8 +18706,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.2">
-      <c r="A85" s="52">
+    <row r="85" spans="1:27" ht="19.149999999999999">
+      <c r="A85" s="38">
         <v>8</v>
       </c>
       <c r="B85" s="11" t="s">
@@ -18959,11 +18721,11 @@
       <c r="E85" s="12"/>
       <c r="F85" s="10"/>
       <c r="G85" s="12"/>
-      <c r="H85" s="54">
+      <c r="H85" s="12">
         <f>IF((D85-E85)&lt;0,0,(D85-E85))</f>
         <v>0</v>
       </c>
-      <c r="I85" s="54">
+      <c r="I85" s="12">
         <f>IF((E85-D85)&lt;0,0,(E85-D85))</f>
         <v>0</v>
       </c>
@@ -19013,12 +18775,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.2">
+    <row r="86" spans="1:27" ht="19.149999999999999">
       <c r="A86" s="10">
         <v>8</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C86" s="10"/>
       <c r="D86" s="12">
@@ -19082,7 +18844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.2">
+    <row r="87" spans="1:27" ht="19.149999999999999">
       <c r="A87" s="10">
         <v>8</v>
       </c>
@@ -19151,12 +18913,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.2">
-      <c r="A88" s="52">
+    <row r="88" spans="1:27" ht="19.149999999999999">
+      <c r="A88" s="38">
         <v>8</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C88" s="12"/>
       <c r="D88" s="12">
@@ -19166,11 +18928,11 @@
       <c r="E88" s="12"/>
       <c r="F88" s="10"/>
       <c r="G88" s="12"/>
-      <c r="H88" s="54">
+      <c r="H88" s="12">
         <f>IF((D88-E88)&lt;0,0,(D88-E88))</f>
         <v>0</v>
       </c>
-      <c r="I88" s="54">
+      <c r="I88" s="12">
         <f>IF((E88-D88)&lt;0,0,(E88-D88))</f>
         <v>0</v>
       </c>
@@ -19220,12 +18982,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.2">
+    <row r="89" spans="1:27" ht="19.149999999999999">
       <c r="A89" s="10">
         <v>8</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="12">
@@ -19289,10 +19051,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" s="7" customFormat="1">
-      <c r="B90" s="48"/>
-    </row>
-    <row r="91" spans="1:27" ht="19.2">
+    <row r="90" spans="1:27" s="7" customFormat="1"/>
+    <row r="91" spans="1:27" ht="19.149999999999999">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -19361,7 +19121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" ht="19.2">
+    <row r="92" spans="1:27" ht="19.149999999999999">
       <c r="A92" s="10">
         <v>9</v>
       </c>
@@ -19430,7 +19190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:27" ht="19.2">
+    <row r="93" spans="1:27" ht="19.149999999999999">
       <c r="A93" s="10">
         <v>9</v>
       </c>
@@ -19499,7 +19259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.2">
+    <row r="94" spans="1:27" ht="19.149999999999999">
       <c r="A94" s="10">
         <v>9</v>
       </c>
@@ -19568,7 +19328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.2">
+    <row r="95" spans="1:27" ht="19.149999999999999">
       <c r="A95" s="10">
         <v>9</v>
       </c>
@@ -19637,7 +19397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.2">
+    <row r="96" spans="1:27" ht="19.149999999999999">
       <c r="A96" s="10">
         <v>9</v>
       </c>
@@ -19706,8 +19466,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.2">
-      <c r="A97" s="52">
+    <row r="97" spans="1:27" ht="19.149999999999999">
+      <c r="A97" s="38">
         <v>9</v>
       </c>
       <c r="B97" s="11" t="s">
@@ -19721,11 +19481,11 @@
       <c r="E97" s="12"/>
       <c r="F97" s="10"/>
       <c r="G97" s="12"/>
-      <c r="H97" s="54">
+      <c r="H97" s="12">
         <f>IF((D97-E97)&lt;0,0,(D97-E97))</f>
         <v>0</v>
       </c>
-      <c r="I97" s="54">
+      <c r="I97" s="12">
         <f>IF((E97-D97)&lt;0,0,(E97-D97))</f>
         <v>0</v>
       </c>
@@ -19775,12 +19535,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.2">
+    <row r="98" spans="1:27" ht="19.149999999999999">
       <c r="A98" s="10">
         <v>9</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C98" s="10"/>
       <c r="D98" s="12">
@@ -19844,7 +19604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.2">
+    <row r="99" spans="1:27" ht="19.149999999999999">
       <c r="A99" s="10">
         <v>9</v>
       </c>
@@ -19913,12 +19673,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.2">
-      <c r="A100" s="52">
+    <row r="100" spans="1:27" ht="19.149999999999999">
+      <c r="A100" s="38">
         <v>9</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C100" s="10"/>
       <c r="D100" s="12">
@@ -19928,11 +19688,11 @@
       <c r="E100" s="12"/>
       <c r="F100" s="10"/>
       <c r="G100" s="12"/>
-      <c r="H100" s="54">
+      <c r="H100" s="12">
         <f>IF((D100-E100)&lt;0,0,(D100-E100))</f>
         <v>0</v>
       </c>
-      <c r="I100" s="54">
+      <c r="I100" s="12">
         <f>IF((E100-D100)&lt;0,0,(E100-D100))</f>
         <v>0</v>
       </c>
@@ -19982,12 +19742,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.2">
+    <row r="101" spans="1:27" ht="19.149999999999999">
       <c r="A101" s="10">
         <v>9</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="12">
@@ -20051,10 +19811,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:27" s="7" customFormat="1">
-      <c r="B102" s="48"/>
-    </row>
-    <row r="103" spans="1:27" ht="19.2">
+    <row r="102" spans="1:27" s="7" customFormat="1"/>
+    <row r="103" spans="1:27" ht="19.149999999999999">
       <c r="A103" s="10">
         <v>10</v>
       </c>
@@ -20123,7 +19881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.2">
+    <row r="104" spans="1:27" ht="19.149999999999999">
       <c r="A104" s="10">
         <v>10</v>
       </c>
@@ -20192,7 +19950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.2">
+    <row r="105" spans="1:27" ht="19.149999999999999">
       <c r="A105" s="10">
         <v>10</v>
       </c>
@@ -20261,7 +20019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.2">
+    <row r="106" spans="1:27" ht="19.149999999999999">
       <c r="A106" s="10">
         <v>10</v>
       </c>
@@ -20330,7 +20088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="19.2">
+    <row r="107" spans="1:27" ht="19.149999999999999">
       <c r="A107" s="10">
         <v>10</v>
       </c>
@@ -20399,7 +20157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="19.2">
+    <row r="108" spans="1:27" ht="19.149999999999999">
       <c r="A108" s="10">
         <v>10</v>
       </c>
@@ -20468,8 +20226,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="19.2">
-      <c r="A109" s="52">
+    <row r="109" spans="1:27" ht="19.149999999999999">
+      <c r="A109" s="38">
         <v>10</v>
       </c>
       <c r="B109" s="11" t="s">
@@ -20483,11 +20241,11 @@
       <c r="E109" s="12"/>
       <c r="F109" s="10"/>
       <c r="G109" s="12"/>
-      <c r="H109" s="54">
+      <c r="H109" s="12">
         <f>IF((D109-E109)&lt;0,0,(D109-E109))</f>
         <v>0</v>
       </c>
-      <c r="I109" s="54">
+      <c r="I109" s="12">
         <f>IF((E109-D109)&lt;0,0,(E109-D109))</f>
         <v>0</v>
       </c>
@@ -20537,12 +20295,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="19.2">
+    <row r="110" spans="1:27" ht="19.149999999999999">
       <c r="A110" s="10">
         <v>10</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C110" s="10"/>
       <c r="D110" s="12">
@@ -20606,7 +20364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" ht="19.2">
+    <row r="111" spans="1:27" ht="19.149999999999999">
       <c r="A111" s="10">
         <v>10</v>
       </c>
@@ -20675,12 +20433,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:27" ht="19.2">
-      <c r="A112" s="52">
+    <row r="112" spans="1:27" ht="19.149999999999999">
+      <c r="A112" s="38">
         <v>10</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C112" s="10"/>
       <c r="D112" s="12">
@@ -20690,11 +20448,11 @@
       <c r="E112" s="12"/>
       <c r="F112" s="10"/>
       <c r="G112" s="12"/>
-      <c r="H112" s="54">
+      <c r="H112" s="12">
         <f>IF((D112-E112)&lt;0,0,(D112-E112))</f>
         <v>0</v>
       </c>
-      <c r="I112" s="54">
+      <c r="I112" s="12">
         <f>IF((E112-D112)&lt;0,0,(E112-D112))</f>
         <v>0</v>
       </c>
@@ -20744,12 +20502,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:28" ht="19.2">
+    <row r="113" spans="1:28" ht="19.149999999999999">
       <c r="A113" s="10">
         <v>10</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="12">
@@ -20813,10 +20571,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:28" s="7" customFormat="1">
-      <c r="B114" s="48"/>
-    </row>
-    <row r="115" spans="1:28" ht="38.4">
+    <row r="114" spans="1:28" s="7" customFormat="1"/>
+    <row r="115" spans="1:28" ht="38.450000000000003">
       <c r="A115" s="1" t="s">
         <v>23</v>
       </c>
@@ -20885,7 +20641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:28" ht="19.2">
+    <row r="116" spans="1:28" ht="19.149999999999999">
       <c r="A116" s="1" t="s">
         <v>23</v>
       </c>
@@ -20954,7 +20710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:28" ht="19.2">
+    <row r="117" spans="1:28" ht="19.149999999999999">
       <c r="A117" s="1" t="s">
         <v>23</v>
       </c>
@@ -21023,7 +20779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:28" ht="19.2">
+    <row r="118" spans="1:28" ht="19.149999999999999">
       <c r="A118" s="1" t="s">
         <v>23</v>
       </c>
@@ -21092,7 +20848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:28" ht="38.4">
+    <row r="119" spans="1:28" ht="38.450000000000003">
       <c r="A119" s="1" t="s">
         <v>23</v>
       </c>
@@ -21161,7 +20917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:28" ht="19.2">
+    <row r="120" spans="1:28" ht="19.149999999999999">
       <c r="A120" s="1" t="s">
         <v>23</v>
       </c>
@@ -21230,7 +20986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:28" ht="38.4">
+    <row r="121" spans="1:28" ht="38.450000000000003">
       <c r="A121" s="1" t="s">
         <v>23</v>
       </c>
@@ -21299,7 +21055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:28" ht="38.4">
+    <row r="122" spans="1:28" ht="38.450000000000003">
       <c r="A122" s="1" t="s">
         <v>23</v>
       </c>
@@ -21368,12 +21124,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:28" s="7" customFormat="1">
-      <c r="B123" s="48"/>
-    </row>
+    <row r="123" spans="1:28" s="7" customFormat="1"/>
     <row r="124" spans="1:28">
       <c r="A124" s="7"/>
-      <c r="B124" s="48"/>
+      <c r="B124" s="7"/>
       <c r="C124" s="7"/>
       <c r="D124" s="7"/>
       <c r="E124" s="7"/>
@@ -21403,7 +21157,7 @@
     </row>
     <row r="125" spans="1:28">
       <c r="A125" s="7"/>
-      <c r="B125" s="48"/>
+      <c r="B125" s="7"/>
       <c r="C125" s="7"/>
       <c r="D125" s="7"/>
       <c r="E125" s="7"/>
@@ -21433,7 +21187,7 @@
     </row>
     <row r="126" spans="1:28">
       <c r="A126" s="7"/>
-      <c r="B126" s="48"/>
+      <c r="B126" s="7"/>
       <c r="C126" s="7"/>
       <c r="D126" s="7"/>
       <c r="E126" s="7"/>
@@ -21463,7 +21217,7 @@
     </row>
     <row r="127" spans="1:28">
       <c r="A127" s="7"/>
-      <c r="B127" s="48"/>
+      <c r="B127" s="7"/>
       <c r="C127" s="7"/>
       <c r="D127" s="7"/>
       <c r="E127" s="7"/>
@@ -21493,7 +21247,7 @@
     </row>
     <row r="128" spans="1:28">
       <c r="A128" s="7"/>
-      <c r="B128" s="48"/>
+      <c r="B128" s="7"/>
       <c r="C128" s="7"/>
       <c r="D128" s="7"/>
       <c r="E128" s="7"/>
@@ -21523,7 +21277,7 @@
     </row>
     <row r="129" spans="1:28">
       <c r="A129" s="7"/>
-      <c r="B129" s="48"/>
+      <c r="B129" s="7"/>
       <c r="C129" s="7"/>
       <c r="D129" s="7"/>
       <c r="E129" s="7"/>
@@ -21553,7 +21307,7 @@
     </row>
     <row r="130" spans="1:28">
       <c r="A130" s="7"/>
-      <c r="B130" s="48"/>
+      <c r="B130" s="7"/>
       <c r="C130" s="7"/>
       <c r="D130" s="7"/>
       <c r="E130" s="7"/>
@@ -21583,7 +21337,7 @@
     </row>
     <row r="131" spans="1:28">
       <c r="A131" s="7"/>
-      <c r="B131" s="48"/>
+      <c r="B131" s="7"/>
       <c r="C131" s="7"/>
       <c r="D131" s="7"/>
       <c r="E131" s="7"/>
@@ -21613,7 +21367,7 @@
     </row>
     <row r="132" spans="1:28">
       <c r="A132" s="7"/>
-      <c r="B132" s="48"/>
+      <c r="B132" s="7"/>
       <c r="C132" s="7"/>
       <c r="D132" s="7"/>
       <c r="E132" s="7"/>
@@ -21643,7 +21397,7 @@
     </row>
     <row r="133" spans="1:28">
       <c r="A133" s="7"/>
-      <c r="B133" s="48"/>
+      <c r="B133" s="7"/>
       <c r="C133" s="7"/>
       <c r="D133" s="7"/>
       <c r="E133" s="7"/>
@@ -21673,7 +21427,7 @@
     </row>
     <row r="134" spans="1:28">
       <c r="A134" s="7"/>
-      <c r="B134" s="48"/>
+      <c r="B134" s="7"/>
       <c r="C134" s="7"/>
       <c r="D134" s="7"/>
       <c r="E134" s="7"/>
@@ -21703,7 +21457,7 @@
     </row>
     <row r="135" spans="1:28">
       <c r="A135" s="7"/>
-      <c r="B135" s="48"/>
+      <c r="B135" s="7"/>
       <c r="C135" s="7"/>
       <c r="D135" s="7"/>
       <c r="E135" s="7"/>
@@ -21733,7 +21487,7 @@
     </row>
     <row r="136" spans="1:28">
       <c r="A136" s="7"/>
-      <c r="B136" s="48"/>
+      <c r="B136" s="7"/>
       <c r="C136" s="7"/>
       <c r="D136" s="7"/>
       <c r="E136" s="7"/>
@@ -21763,7 +21517,7 @@
     </row>
     <row r="137" spans="1:28">
       <c r="A137" s="7"/>
-      <c r="B137" s="48"/>
+      <c r="B137" s="7"/>
       <c r="C137" s="7"/>
       <c r="D137" s="7"/>
       <c r="E137" s="7"/>
@@ -21793,7 +21547,7 @@
     </row>
     <row r="138" spans="1:28">
       <c r="A138" s="7"/>
-      <c r="B138" s="48"/>
+      <c r="B138" s="7"/>
       <c r="C138" s="7"/>
       <c r="D138" s="7"/>
       <c r="E138" s="7"/>
@@ -21823,7 +21577,7 @@
     </row>
     <row r="139" spans="1:28">
       <c r="A139" s="7"/>
-      <c r="B139" s="48"/>
+      <c r="B139" s="7"/>
       <c r="C139" s="7"/>
       <c r="D139" s="7"/>
       <c r="E139" s="7"/>
@@ -21853,7 +21607,7 @@
     </row>
     <row r="140" spans="1:28">
       <c r="A140" s="7"/>
-      <c r="B140" s="48"/>
+      <c r="B140" s="7"/>
       <c r="C140" s="7"/>
       <c r="D140" s="7"/>
       <c r="E140" s="7"/>
@@ -21881,186 +21635,6 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101" name="Textbooks"/>
@@ -22074,12 +21648,21 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X115:X122" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025  , 2026"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F10 F12:F19 F21:F29 F31:F41 F43:F53 F55:F65 F67:F77 F79:F89 F91:F101 F103:F113 F115:F122 L3:L10 L12:L19 L21:L29 L31:L41 L43:L53 L55:L65 L67:L77 L79:L89 L91:L101 L103:L113 L115:L122 R3:R10 R12:R19 R21:R29 R31:R41 R43:R53 R55:R65 R67:R77 R79:R89 R91:R101 R103:R113 R115:R122" xr:uid="{5A71FB48-8EAE-4DFD-A74E-6E5D7EC0989F}">
+      <formula1>"2024,2025 ,2026"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X3:X10" xr:uid="{100CB7E3-98D1-421C-B2B8-D90C577AB9E8}">
+      <formula1>"2024,2025 , 2026"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X12:X19 X21:X29 X31:X41 X43:X53 X55:X65 X67:X77 X79:X89 X91:X101 X103:X113" xr:uid="{9394C4D3-5674-419D-8718-7D81EDF4656F}">
+      <formula1>"2024,2025  , 2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel-files/MARIKINA/PAMANTASAN NG LUNGSOD NG MARIKINA.xlsx
+++ b/excel-files/MARIKINA/PAMANTASAN NG LUNGSOD NG MARIKINA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29825"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29930"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="107" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{118C1C40-8ECA-4B49-8BDC-77A8FC994FB7}"/>
+  <xr:revisionPtr revIDLastSave="108" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{686C4E2A-AA0A-4E30-9435-E780EAF466F5}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -5183,11 +5183,10 @@
       <c r="E91" s="1"/>
       <c r="F91" s="5"/>
       <c r="G91" s="3">
-        <f t="shared" ref="G91:G98" si="18">IF((C91-D91)&lt;0,0,C91-D91)</f>
         <v>0</v>
       </c>
       <c r="H91" s="4">
-        <f t="shared" ref="H91:H98" si="19">IF((D91-C91)&lt;0,0,D91-C91)</f>
+        <f t="shared" ref="H91:H98" si="18">IF((D91-C91)&lt;0,0,D91-C91)</f>
         <v>0</v>
       </c>
     </row>
@@ -5203,11 +5202,11 @@
       <c r="E92" s="1"/>
       <c r="F92" s="5"/>
       <c r="G92" s="3">
+        <f t="shared" ref="G91:G98" si="19">IF((C92-D92)&lt;0,0,C92-D92)</f>
+        <v>0</v>
+      </c>
+      <c r="H92" s="4">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="H92" s="4">
-        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -5223,11 +5222,11 @@
       <c r="E93" s="1"/>
       <c r="F93" s="5"/>
       <c r="G93" s="3">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="H93" s="4">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="H93" s="4">
-        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -5243,11 +5242,11 @@
       <c r="E94" s="1"/>
       <c r="F94" s="5"/>
       <c r="G94" s="3">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="H94" s="4">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="H94" s="4">
-        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -5263,11 +5262,11 @@
       <c r="E95" s="1"/>
       <c r="F95" s="5"/>
       <c r="G95" s="3">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="H95" s="4">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="H95" s="4">
-        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -5283,11 +5282,11 @@
       <c r="E96" s="1"/>
       <c r="F96" s="5"/>
       <c r="G96" s="3">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="H96" s="4">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="H96" s="4">
-        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -5303,11 +5302,11 @@
       <c r="E97" s="1"/>
       <c r="F97" s="5"/>
       <c r="G97" s="3">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="H97" s="4">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="H97" s="4">
-        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -5323,11 +5322,11 @@
       <c r="E98" s="1"/>
       <c r="F98" s="5"/>
       <c r="G98" s="3">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="H98" s="4">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="H98" s="4">
-        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -21648,11 +21647,11 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="5">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X115:X122" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X115:X122 X12:X19 X21:X29 X31:X41 X43:X53 X55:X65 X67:X77 X79:X89 X91:X101 X103:X113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
       <formula1>"2024,2025  , 2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F10 F12:F19 F21:F29 F31:F41 F43:F53 F55:F65 F67:F77 F79:F89 F91:F101 F103:F113 F115:F122 L3:L10 L12:L19 L21:L29 L31:L41 L43:L53 L55:L65 L67:L77 L79:L89 L91:L101 L103:L113 L115:L122 R3:R10 R12:R19 R21:R29 R31:R41 R43:R53 R55:R65 R67:R77 R79:R89 R91:R101 R103:R113 R115:R122" xr:uid="{5A71FB48-8EAE-4DFD-A74E-6E5D7EC0989F}">
@@ -21660,9 +21659,6 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X3:X10" xr:uid="{100CB7E3-98D1-421C-B2B8-D90C577AB9E8}">
       <formula1>"2024,2025 , 2026"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X12:X19 X21:X29 X31:X41 X43:X53 X55:X65 X67:X77 X79:X89 X91:X101 X103:X113" xr:uid="{9394C4D3-5674-419D-8718-7D81EDF4656F}">
-      <formula1>"2024,2025  , 2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
